--- a/data/existing/판매중_상품구성_사업방법서_매핑.xlsx
+++ b/data/existing/판매중_상품구성_사업방법서_매핑.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\회사\문서자동화\사전자료\기준정보_260308\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\claudecsw\ruleautomatker\data\existing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14AB9043-5EF7-4832-B167-E5ABF933AEEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B446EF73-745F-4799-BCEC-BE4908B534A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{364CA86F-2012-40A9-A884-5853FC3C1200}"/>
+    <workbookView xWindow="51480" yWindow="30" windowWidth="51840" windowHeight="21120" xr2:uid="{364CA86F-2012-40A9-A884-5853FC3C1200}"/>
   </bookViews>
   <sheets>
     <sheet name="보종코드_상품코드_매핑" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">보종코드_상품코드_매핑!$A$1:$H$262</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">보종코드_상품코드_매핑!$A$1:$I$262</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="457">
   <si>
     <t>ISRN_KIND_DTCD</t>
   </si>
@@ -1275,133 +1275,142 @@
     <t>한화생명 H종신보험 무배당_사업방법서_20260101~.pdf</t>
   </si>
   <si>
+    <t>한화생명 Wealth단체저축보험 무배당_사업방법서_20260101~.pdf</t>
+  </si>
+  <si>
+    <t>한화생명 Wealth직장인연금보험 무배당_사업방법서_20260130~.pdf</t>
+  </si>
+  <si>
+    <t>한화생명 간편가입 H당뇨보험 무배당_사업방법서_20260101~.pdf</t>
+  </si>
+  <si>
+    <t>한화생명 간편가입 H종신보험 무배당_사업방법서_20260101~.pdf</t>
+  </si>
+  <si>
+    <t>한화생명 간편가입 Need AI 암보험 무배당_사업방법서_20260101~.pdf</t>
+  </si>
+  <si>
+    <t>한화생명 간편가입 경영인H정기보험 무배당_사업방법서_20260101~.pdf</t>
+  </si>
+  <si>
+    <t>한화생명 간편가입 상속H종신보험 무배당_사업방법서_20260101~.pdf</t>
+  </si>
+  <si>
+    <t>한화생명 간편가입 시그니처H보장보험 무배당_사업방법서_20260101~.pdf</t>
+  </si>
+  <si>
+    <t>한화생명 간편가입 시그니처H암보험 무배당_사업방법서_20260101~.pdf</t>
+  </si>
+  <si>
+    <t>한화생명 간편가입 실손의료비보장보험(갱신형) 무배당(재가입용)_사업방법서_20260101~.pdf</t>
+  </si>
+  <si>
+    <t>한화생명 간편가입 제로백H종신보험 무배당_사업방법서_20260201~.pdf</t>
+  </si>
+  <si>
+    <t>한화생명 간편가입 포켓골절보험 무배당_사업방법서_20260101~.pdf</t>
+  </si>
+  <si>
+    <t>한화생명 간편가입 하나로H종신보험 무배당_사업방법서_20260101~.pdf</t>
+  </si>
+  <si>
+    <t>한화생명 경영인H정기보험 무배당_사업방법서_20260101~.pdf</t>
+  </si>
+  <si>
+    <t>한화생명 기본형 급여 e실손의료비보장보험(갱신형) 무배당_사업방법서_20260101~.pdf</t>
+  </si>
+  <si>
+    <t>한화생명 기본형 급여 실손의료비보장보험(갱신형) 무배당_사업방법서_20260101~.pdf</t>
+  </si>
+  <si>
+    <t>한화생명 기본형 급여 실손의료비보장보험(계약전환 단체개인전환 개인중지재개용)(갱신형) 무배당_사업방법서_20260101~.pdf</t>
+  </si>
+  <si>
+    <t>한화생명 기업복지라이프플랜보험 무배당_사업방법서_20260101~.pdf</t>
+  </si>
+  <si>
+    <t>한화생명 노후실손의료비보장보험(갱신형) 무배당_사업방법서_20260101~.pdf</t>
+  </si>
+  <si>
+    <t>한화생명 바로연금보험 무배당_사업방법서_20260101~.pdf</t>
+  </si>
+  <si>
+    <t>한화생명 상생친구 보장보험 무배당_사업방법서_20260201~.pdf</t>
+  </si>
+  <si>
+    <t>한화생명 상속H종신보험 무배당_사업방법서_20260101~.pdf</t>
+  </si>
+  <si>
+    <t>한화생명 스마트H상해보험 무배당_사업방법서_20260201~.pdf</t>
+  </si>
+  <si>
+    <t>한화생명 스마트V상해보험 무배당_사업방법서_20260201~.pdf</t>
+  </si>
+  <si>
+    <t>한화생명 스마트V연금보험 무배당_사업방법서_20260101~.pdf</t>
+  </si>
+  <si>
+    <t>한화생명 스마트하이브리드연금보험 무배당_사업방법서_20260201~.pdf</t>
+  </si>
+  <si>
+    <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형)_사업방법서_20260201~.pdf</t>
+  </si>
+  <si>
+    <t>한화생명 시그니처 H통합건강보험 무배당_사업방법서_20260201~.pdf</t>
+  </si>
+  <si>
+    <t>한화생명 시그니처H보장보험 무배당_사업방법서_20260101~.pdf</t>
+  </si>
+  <si>
+    <t>한화생명 시그니처H암보험 무배당_사업방법서_20260101~.pdf</t>
+  </si>
+  <si>
+    <t>한화생명 연금보험Enterprise 무배당_사업방법서_20260101~.pdf</t>
+  </si>
+  <si>
+    <t>한화생명 연금저축 미래로기업복지연금보험_사업방법서_20260101~.pdf</t>
+  </si>
+  <si>
+    <t>한화생명 연금저축 스마트하이드림연금보험_사업방법서_20260101~.pdf</t>
+  </si>
+  <si>
+    <t>한화생명 연금저축 하이드림연금보험_사업방법서_20260101~.pdf</t>
+  </si>
+  <si>
+    <t>한화생명 장애인전용 곰두리보장보험 무배당_사업방법서_20260101~.pdf</t>
+  </si>
+  <si>
+    <t>한화생명 제로백H종신보험 무배당_사업방법서_20260201~.pdf</t>
+  </si>
+  <si>
+    <t>한화생명 진심가득H보장보험 무배당_사업방법서_20260201~.pdf</t>
+  </si>
+  <si>
+    <t>한화생명 케어백간병플러스보험 무배당_사업방법서_20260101~.pdf</t>
+  </si>
+  <si>
+    <t>한화생명 튼튼이 치아보험(갱신형) 무배당_사업방법서_20260101~.pdf</t>
+  </si>
+  <si>
+    <t>한화생명 포켓골절보험 무배당_사업방법서_20260101~.pdf</t>
+  </si>
+  <si>
+    <t>한화생명 하나로H종신보험 무배당_사업방법서_20260101~.pdf</t>
+  </si>
+  <si>
+    <t>사업방법서 파일명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>한화생명 상속H종신보험 무배당_사업방법서_20260101~.pdf</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>한화생명 Need AI 암보험 무배당_사업방법서_20260101~.pdf</t>
-  </si>
-  <si>
-    <t>한화생명 Wealth단체저축보험 무배당_사업방법서_20260101~.pdf</t>
-  </si>
-  <si>
-    <t>한화생명 Wealth직장인연금보험 무배당_사업방법서_20260130~.pdf</t>
-  </si>
-  <si>
-    <t>한화생명 간편가입 H당뇨보험 무배당_사업방법서_20260101~.pdf</t>
-  </si>
-  <si>
-    <t>한화생명 간편가입 H종신보험 무배당_사업방법서_20260101~.pdf</t>
-  </si>
-  <si>
-    <t>한화생명 간편가입 Need AI 암보험 무배당_사업방법서_20260101~.pdf</t>
-  </si>
-  <si>
-    <t>한화생명 간편가입 경영인H정기보험 무배당_사업방법서_20260101~.pdf</t>
-  </si>
-  <si>
-    <t>한화생명 간편가입 상속H종신보험 무배당_사업방법서_20260101~.pdf</t>
-  </si>
-  <si>
-    <t>한화생명 간편가입 시그니처H보장보험 무배당_사업방법서_20260101~.pdf</t>
-  </si>
-  <si>
-    <t>한화생명 간편가입 시그니처H암보험 무배당_사업방법서_20260101~.pdf</t>
-  </si>
-  <si>
-    <t>한화생명 간편가입 실손의료비보장보험(갱신형) 무배당(재가입용)_사업방법서_20260101~.pdf</t>
-  </si>
-  <si>
-    <t>한화생명 간편가입 제로백H종신보험 무배당_사업방법서_20260201~.pdf</t>
-  </si>
-  <si>
-    <t>한화생명 간편가입 포켓골절보험 무배당_사업방법서_20260101~.pdf</t>
-  </si>
-  <si>
-    <t>한화생명 간편가입 하나로H종신보험 무배당_사업방법서_20260101~.pdf</t>
-  </si>
-  <si>
-    <t>한화생명 경영인H정기보험 무배당_사업방법서_20260101~.pdf</t>
-  </si>
-  <si>
-    <t>한화생명 기본형 급여 e실손의료비보장보험(갱신형) 무배당_사업방법서_20260101~.pdf</t>
-  </si>
-  <si>
-    <t>한화생명 기본형 급여 실손의료비보장보험(갱신형) 무배당_사업방법서_20260101~.pdf</t>
-  </si>
-  <si>
-    <t>한화생명 기본형 급여 실손의료비보장보험(계약전환 단체개인전환 개인중지재개용)(갱신형) 무배당_사업방법서_20260101~.pdf</t>
-  </si>
-  <si>
-    <t>한화생명 기업복지라이프플랜보험 무배당_사업방법서_20260101~.pdf</t>
-  </si>
-  <si>
-    <t>한화생명 노후실손의료비보장보험(갱신형) 무배당_사업방법서_20260101~.pdf</t>
-  </si>
-  <si>
-    <t>한화생명 바로연금보험 무배당_사업방법서_20260101~.pdf</t>
-  </si>
-  <si>
-    <t>한화생명 상생친구 보장보험 무배당_사업방법서_20260201~.pdf</t>
-  </si>
-  <si>
-    <t>한화생명 상속H종신보험 무배당_사업방법서_20260101~.pdf</t>
-  </si>
-  <si>
-    <t>한화생명 스마트H상해보험 무배당_사업방법서_20260201~.pdf</t>
-  </si>
-  <si>
-    <t>한화생명 스마트V상해보험 무배당_사업방법서_20260201~.pdf</t>
-  </si>
-  <si>
-    <t>한화생명 스마트V연금보험 무배당_사업방법서_20260101~.pdf</t>
-  </si>
-  <si>
-    <t>한화생명 스마트하이브리드연금보험 무배당_사업방법서_20260201~.pdf</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형)_사업방법서_20260201~.pdf</t>
-  </si>
-  <si>
-    <t>한화생명 시그니처 H통합건강보험 무배당_사업방법서_20260201~.pdf</t>
-  </si>
-  <si>
-    <t>한화생명 시그니처H보장보험 무배당_사업방법서_20260101~.pdf</t>
-  </si>
-  <si>
-    <t>한화생명 시그니처H암보험 무배당_사업방법서_20260101~.pdf</t>
-  </si>
-  <si>
-    <t>한화생명 연금보험Enterprise 무배당_사업방법서_20260101~.pdf</t>
-  </si>
-  <si>
-    <t>한화생명 연금저축 미래로기업복지연금보험_사업방법서_20260101~.pdf</t>
-  </si>
-  <si>
-    <t>한화생명 연금저축 스마트하이드림연금보험_사업방법서_20260101~.pdf</t>
-  </si>
-  <si>
-    <t>한화생명 연금저축 하이드림연금보험_사업방법서_20260101~.pdf</t>
-  </si>
-  <si>
-    <t>한화생명 장애인전용 곰두리보장보험 무배당_사업방법서_20260101~.pdf</t>
-  </si>
-  <si>
-    <t>한화생명 제로백H종신보험 무배당_사업방법서_20260201~.pdf</t>
-  </si>
-  <si>
-    <t>한화생명 진심가득H보장보험 무배당_사업방법서_20260201~.pdf</t>
-  </si>
-  <si>
-    <t>한화생명 케어백간병플러스보험 무배당_사업방법서_20260101~.pdf</t>
-  </si>
-  <si>
-    <t>한화생명 튼튼이 치아보험(갱신형) 무배당_사업방법서_20260101~.pdf</t>
-  </si>
-  <si>
-    <t>한화생명 포켓골절보험 무배당_사업방법서_20260101~.pdf</t>
-  </si>
-  <si>
-    <t>한화생명 하나로H종신보험 무배당_사업방법서_20260101~.pdf</t>
-  </si>
-  <si>
-    <t>사업방법서 파일명</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1775,7 +1784,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AECB136-8215-429B-82E5-8A6B6A669FFB}">
-  <dimension ref="A1:I262"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:N262"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.125" bestFit="1" customWidth="1"/>
@@ -1786,7 +1796,8 @@
     <col min="6" max="6" width="100.375" customWidth="1"/>
     <col min="7" max="7" width="24" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="42" customWidth="1"/>
+    <col min="9" max="9" width="59.5" customWidth="1"/>
+    <col min="14" max="14" width="23.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
@@ -1815,10 +1826,10 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2061</v>
       </c>
@@ -1847,7 +1858,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2061</v>
       </c>
@@ -1876,7 +1887,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1772</v>
       </c>
@@ -1905,7 +1916,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1772</v>
       </c>
@@ -1934,7 +1945,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1772</v>
       </c>
@@ -1963,7 +1974,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1772</v>
       </c>
@@ -1992,7 +2003,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1726</v>
       </c>
@@ -2021,7 +2032,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1726</v>
       </c>
@@ -2050,7 +2061,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1726</v>
       </c>
@@ -2079,7 +2090,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1726</v>
       </c>
@@ -2108,7 +2119,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>1764</v>
       </c>
@@ -2137,7 +2148,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1764</v>
       </c>
@@ -2166,7 +2177,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1764</v>
       </c>
@@ -2195,7 +2206,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1764</v>
       </c>
@@ -2224,7 +2235,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2170</v>
       </c>
@@ -2253,7 +2264,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2170</v>
       </c>
@@ -2282,7 +2293,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2170</v>
       </c>
@@ -2311,7 +2322,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2246</v>
       </c>
@@ -2340,7 +2351,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2246</v>
       </c>
@@ -2369,7 +2380,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2246</v>
       </c>
@@ -2398,7 +2409,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2246</v>
       </c>
@@ -2427,7 +2438,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2246</v>
       </c>
@@ -2456,7 +2467,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>2246</v>
       </c>
@@ -2485,7 +2496,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>2246</v>
       </c>
@@ -2514,7 +2525,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>2246</v>
       </c>
@@ -2543,7 +2554,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>2246</v>
       </c>
@@ -2572,7 +2583,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>2253</v>
       </c>
@@ -2601,7 +2612,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>2170</v>
       </c>
@@ -2630,7 +2641,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>2170</v>
       </c>
@@ -2659,7 +2670,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>2209</v>
       </c>
@@ -2688,7 +2699,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>2209</v>
       </c>
@@ -2717,7 +2728,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>2209</v>
       </c>
@@ -2746,7 +2757,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>2209</v>
       </c>
@@ -2775,7 +2786,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>2209</v>
       </c>
@@ -2804,7 +2815,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>2209</v>
       </c>
@@ -2833,7 +2844,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>2209</v>
       </c>
@@ -2862,7 +2873,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>2209</v>
       </c>
@@ -2891,7 +2902,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>2248</v>
       </c>
@@ -2917,10 +2928,10 @@
         <v>2958465</v>
       </c>
       <c r="I39" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>1796</v>
       </c>
@@ -2946,10 +2957,10 @@
         <v>2958465</v>
       </c>
       <c r="I40" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>1833</v>
       </c>
@@ -2975,10 +2986,10 @@
         <v>2958465</v>
       </c>
       <c r="I41" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>1833</v>
       </c>
@@ -3004,10 +3015,10 @@
         <v>2958465</v>
       </c>
       <c r="I42" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>2254</v>
       </c>
@@ -3033,10 +3044,10 @@
         <v>2958465</v>
       </c>
       <c r="I43" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>2210</v>
       </c>
@@ -3062,10 +3073,10 @@
         <v>2958465</v>
       </c>
       <c r="I44" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>2210</v>
       </c>
@@ -3091,10 +3102,10 @@
         <v>2958465</v>
       </c>
       <c r="I45" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>2210</v>
       </c>
@@ -3120,10 +3131,10 @@
         <v>2958465</v>
       </c>
       <c r="I46" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>2210</v>
       </c>
@@ -3149,10 +3160,10 @@
         <v>2958465</v>
       </c>
       <c r="I47" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>2249</v>
       </c>
@@ -3178,10 +3189,10 @@
         <v>2958465</v>
       </c>
       <c r="I48" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>2249</v>
       </c>
@@ -3207,10 +3218,10 @@
         <v>2958465</v>
       </c>
       <c r="I49" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>2243</v>
       </c>
@@ -3236,10 +3247,10 @@
         <v>2958465</v>
       </c>
       <c r="I50" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>2243</v>
       </c>
@@ -3265,10 +3276,10 @@
         <v>2958465</v>
       </c>
       <c r="I51" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>2130</v>
       </c>
@@ -3294,10 +3305,10 @@
         <v>2958465</v>
       </c>
       <c r="I52" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>2130</v>
       </c>
@@ -3323,10 +3334,10 @@
         <v>2958465</v>
       </c>
       <c r="I53" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>2205</v>
       </c>
@@ -3352,10 +3363,10 @@
         <v>2958465</v>
       </c>
       <c r="I54" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>2205</v>
       </c>
@@ -3381,10 +3392,10 @@
         <v>2958465</v>
       </c>
       <c r="I55" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>1976</v>
       </c>
@@ -3410,10 +3421,10 @@
         <v>2958465</v>
       </c>
       <c r="I56" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>1976</v>
       </c>
@@ -3439,10 +3450,10 @@
         <v>2958465</v>
       </c>
       <c r="I57" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>1976</v>
       </c>
@@ -3468,10 +3479,10 @@
         <v>2958465</v>
       </c>
       <c r="I58" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>1976</v>
       </c>
@@ -3497,10 +3508,10 @@
         <v>2958465</v>
       </c>
       <c r="I59" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>2208</v>
       </c>
@@ -3526,10 +3537,10 @@
         <v>2958465</v>
       </c>
       <c r="I60" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>2208</v>
       </c>
@@ -3555,10 +3566,10 @@
         <v>2958465</v>
       </c>
       <c r="I61" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>2256</v>
       </c>
@@ -3584,10 +3595,10 @@
         <v>2958465</v>
       </c>
       <c r="I62" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>2251</v>
       </c>
@@ -3613,10 +3624,10 @@
         <v>2958465</v>
       </c>
       <c r="I63" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>2251</v>
       </c>
@@ -3642,10 +3653,10 @@
         <v>2958465</v>
       </c>
       <c r="I64" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>2251</v>
       </c>
@@ -3671,10 +3682,10 @@
         <v>2958465</v>
       </c>
       <c r="I65" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>2242</v>
       </c>
@@ -3700,10 +3711,10 @@
         <v>2958465</v>
       </c>
       <c r="I66" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>2242</v>
       </c>
@@ -3729,10 +3740,10 @@
         <v>2958465</v>
       </c>
       <c r="I67" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>2242</v>
       </c>
@@ -3758,10 +3769,10 @@
         <v>2958465</v>
       </c>
       <c r="I68" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>2242</v>
       </c>
@@ -3787,10 +3798,10 @@
         <v>2958465</v>
       </c>
       <c r="I69" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>1983</v>
       </c>
@@ -3816,10 +3827,10 @@
         <v>2958465</v>
       </c>
       <c r="I70" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>1983</v>
       </c>
@@ -3845,10 +3856,10 @@
         <v>2958465</v>
       </c>
       <c r="I71" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>1982</v>
       </c>
@@ -3874,10 +3885,10 @@
         <v>2958465</v>
       </c>
       <c r="I72" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>1982</v>
       </c>
@@ -3903,10 +3914,10 @@
         <v>2958465</v>
       </c>
       <c r="I73" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>1982</v>
       </c>
@@ -3932,10 +3943,10 @@
         <v>2958465</v>
       </c>
       <c r="I74" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>1982</v>
       </c>
@@ -3961,10 +3972,10 @@
         <v>2958465</v>
       </c>
       <c r="I75" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>1984</v>
       </c>
@@ -3990,10 +4001,10 @@
         <v>2958465</v>
       </c>
       <c r="I76" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>1984</v>
       </c>
@@ -4019,10 +4030,10 @@
         <v>2958465</v>
       </c>
       <c r="I77" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>1984</v>
       </c>
@@ -4048,10 +4059,10 @@
         <v>2958465</v>
       </c>
       <c r="I78" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>1984</v>
       </c>
@@ -4077,10 +4088,10 @@
         <v>2958465</v>
       </c>
       <c r="I79" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>1984</v>
       </c>
@@ -4106,10 +4117,10 @@
         <v>2958465</v>
       </c>
       <c r="I80" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>1984</v>
       </c>
@@ -4135,10 +4146,10 @@
         <v>2958465</v>
       </c>
       <c r="I81" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>1984</v>
       </c>
@@ -4164,10 +4175,10 @@
         <v>2958465</v>
       </c>
       <c r="I82" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>1984</v>
       </c>
@@ -4193,10 +4204,10 @@
         <v>2958465</v>
       </c>
       <c r="I83" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>1985</v>
       </c>
@@ -4222,10 +4233,10 @@
         <v>2958465</v>
       </c>
       <c r="I84" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>1985</v>
       </c>
@@ -4251,10 +4262,10 @@
         <v>2958465</v>
       </c>
       <c r="I85" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>1985</v>
       </c>
@@ -4280,10 +4291,10 @@
         <v>2958465</v>
       </c>
       <c r="I86" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>1985</v>
       </c>
@@ -4309,10 +4320,10 @@
         <v>2958465</v>
       </c>
       <c r="I87" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>1986</v>
       </c>
@@ -4338,10 +4349,10 @@
         <v>2958465</v>
       </c>
       <c r="I88" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>1986</v>
       </c>
@@ -4367,10 +4378,10 @@
         <v>2958465</v>
       </c>
       <c r="I89" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>1224</v>
       </c>
@@ -4396,10 +4407,10 @@
         <v>2958465</v>
       </c>
       <c r="I90" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>1224</v>
       </c>
@@ -4425,10 +4436,10 @@
         <v>2958465</v>
       </c>
       <c r="I91" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>1808</v>
       </c>
@@ -4454,10 +4465,10 @@
         <v>2958465</v>
       </c>
       <c r="I92" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>1808</v>
       </c>
@@ -4483,10 +4494,10 @@
         <v>2958465</v>
       </c>
       <c r="I93" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>1946</v>
       </c>
@@ -4512,10 +4523,10 @@
         <v>2958465</v>
       </c>
       <c r="I94" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>1946</v>
       </c>
@@ -4541,10 +4552,10 @@
         <v>2958465</v>
       </c>
       <c r="I95" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>2259</v>
       </c>
@@ -4570,10 +4581,10 @@
         <v>2958465</v>
       </c>
       <c r="I96" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>2259</v>
       </c>
@@ -4599,10 +4610,10 @@
         <v>2958465</v>
       </c>
       <c r="I97" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>2259</v>
       </c>
@@ -4628,10 +4639,10 @@
         <v>2958465</v>
       </c>
       <c r="I98" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>2259</v>
       </c>
@@ -4657,10 +4668,10 @@
         <v>2958465</v>
       </c>
       <c r="I99" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>2259</v>
       </c>
@@ -4686,10 +4697,10 @@
         <v>2958465</v>
       </c>
       <c r="I100" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>2259</v>
       </c>
@@ -4715,10 +4726,10 @@
         <v>2958465</v>
       </c>
       <c r="I101" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>2259</v>
       </c>
@@ -4744,10 +4755,10 @@
         <v>2958465</v>
       </c>
       <c r="I102" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>2259</v>
       </c>
@@ -4773,10 +4784,10 @@
         <v>2958465</v>
       </c>
       <c r="I103" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>2259</v>
       </c>
@@ -4802,10 +4813,10 @@
         <v>2958465</v>
       </c>
       <c r="I104" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>2259</v>
       </c>
@@ -4831,10 +4842,10 @@
         <v>2958465</v>
       </c>
       <c r="I105" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>2259</v>
       </c>
@@ -4860,10 +4871,10 @@
         <v>2958465</v>
       </c>
       <c r="I106" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>2259</v>
       </c>
@@ -4889,10 +4900,10 @@
         <v>2958465</v>
       </c>
       <c r="I107" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>2259</v>
       </c>
@@ -4918,10 +4929,10 @@
         <v>2958465</v>
       </c>
       <c r="I108" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>2259</v>
       </c>
@@ -4947,10 +4958,10 @@
         <v>2958465</v>
       </c>
       <c r="I109" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>2259</v>
       </c>
@@ -4976,10 +4987,10 @@
         <v>2958465</v>
       </c>
       <c r="I110" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>2259</v>
       </c>
@@ -5005,10 +5016,10 @@
         <v>2958465</v>
       </c>
       <c r="I111" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>2259</v>
       </c>
@@ -5034,10 +5045,10 @@
         <v>2958465</v>
       </c>
       <c r="I112" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>2259</v>
       </c>
@@ -5063,10 +5074,10 @@
         <v>2958465</v>
       </c>
       <c r="I113" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>2259</v>
       </c>
@@ -5092,10 +5103,10 @@
         <v>2958465</v>
       </c>
       <c r="I114" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>2259</v>
       </c>
@@ -5121,10 +5132,10 @@
         <v>2958465</v>
       </c>
       <c r="I115" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>2259</v>
       </c>
@@ -5150,10 +5161,10 @@
         <v>2958465</v>
       </c>
       <c r="I116" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>2259</v>
       </c>
@@ -5179,10 +5190,10 @@
         <v>2958465</v>
       </c>
       <c r="I117" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>2126</v>
       </c>
@@ -5208,10 +5219,10 @@
         <v>2958465</v>
       </c>
       <c r="I118" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>2126</v>
       </c>
@@ -5237,10 +5248,10 @@
         <v>2958465</v>
       </c>
       <c r="I119" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>2126</v>
       </c>
@@ -5266,10 +5277,10 @@
         <v>2958465</v>
       </c>
       <c r="I120" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>2129</v>
       </c>
@@ -5295,10 +5306,10 @@
         <v>2958465</v>
       </c>
       <c r="I121" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>2129</v>
       </c>
@@ -5324,10 +5335,10 @@
         <v>2958465</v>
       </c>
       <c r="I122" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>2129</v>
       </c>
@@ -5353,10 +5364,10 @@
         <v>2958465</v>
       </c>
       <c r="I123" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>2129</v>
       </c>
@@ -5382,10 +5393,10 @@
         <v>2958465</v>
       </c>
       <c r="I124" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>2236</v>
       </c>
@@ -5411,10 +5422,10 @@
         <v>2958465</v>
       </c>
       <c r="I125" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>2236</v>
       </c>
@@ -5440,10 +5451,10 @@
         <v>2958465</v>
       </c>
       <c r="I126" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>2236</v>
       </c>
@@ -5469,10 +5480,10 @@
         <v>2958465</v>
       </c>
       <c r="I127" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>2236</v>
       </c>
@@ -5498,10 +5509,10 @@
         <v>2958465</v>
       </c>
       <c r="I128" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="129" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>1758</v>
       </c>
@@ -5527,10 +5538,10 @@
         <v>2958465</v>
       </c>
       <c r="I129" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="130" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>1758</v>
       </c>
@@ -5556,10 +5567,10 @@
         <v>2958465</v>
       </c>
       <c r="I130" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="131" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>1758</v>
       </c>
@@ -5585,10 +5596,10 @@
         <v>2958465</v>
       </c>
       <c r="I131" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="132" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>1758</v>
       </c>
@@ -5614,10 +5625,10 @@
         <v>2958465</v>
       </c>
       <c r="I132" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="133" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>1758</v>
       </c>
@@ -5643,10 +5654,10 @@
         <v>2958465</v>
       </c>
       <c r="I133" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="134" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>2042</v>
       </c>
@@ -5672,10 +5683,10 @@
         <v>2958465</v>
       </c>
       <c r="I134" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="135" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>2042</v>
       </c>
@@ -5701,10 +5712,10 @@
         <v>2958465</v>
       </c>
       <c r="I135" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="136" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>2042</v>
       </c>
@@ -5730,10 +5741,10 @@
         <v>2958465</v>
       </c>
       <c r="I136" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="137" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>2042</v>
       </c>
@@ -5759,10 +5770,10 @@
         <v>2958465</v>
       </c>
       <c r="I137" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="138" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>2042</v>
       </c>
@@ -5788,10 +5799,10 @@
         <v>2958465</v>
       </c>
       <c r="I138" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="139" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>2258</v>
       </c>
@@ -5817,10 +5828,10 @@
         <v>2958465</v>
       </c>
       <c r="I139" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="140" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>2258</v>
       </c>
@@ -5846,10 +5857,17 @@
         <v>2958465</v>
       </c>
       <c r="I140" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
+        <v>438</v>
+      </c>
+      <c r="M140">
+        <f>IF(I139=N140,1,2)</f>
+        <v>1</v>
+      </c>
+      <c r="N140" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="141" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>2258</v>
       </c>
@@ -5875,10 +5893,10 @@
         <v>2958465</v>
       </c>
       <c r="I141" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="142" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>2258</v>
       </c>
@@ -5904,10 +5922,10 @@
         <v>2958465</v>
       </c>
       <c r="I142" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="143" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>2258</v>
       </c>
@@ -5933,10 +5951,10 @@
         <v>2958465</v>
       </c>
       <c r="I143" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="144" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>2258</v>
       </c>
@@ -5962,7 +5980,7 @@
         <v>2958465</v>
       </c>
       <c r="I144" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.3">
@@ -5991,7 +6009,7 @@
         <v>2958465</v>
       </c>
       <c r="I145" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.3">
@@ -6020,7 +6038,7 @@
         <v>2958465</v>
       </c>
       <c r="I146" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.3">
@@ -6049,7 +6067,7 @@
         <v>2958465</v>
       </c>
       <c r="I147" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.3">
@@ -6078,7 +6096,7 @@
         <v>2958465</v>
       </c>
       <c r="I148" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.3">
@@ -6107,7 +6125,7 @@
         <v>2958465</v>
       </c>
       <c r="I149" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.3">
@@ -6136,7 +6154,7 @@
         <v>2958465</v>
       </c>
       <c r="I150" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.3">
@@ -6165,10 +6183,10 @@
         <v>2958465</v>
       </c>
       <c r="I151" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>2257</v>
       </c>
@@ -6194,10 +6212,10 @@
         <v>2958465</v>
       </c>
       <c r="I152" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>2257</v>
       </c>
@@ -6223,10 +6241,10 @@
         <v>2958465</v>
       </c>
       <c r="I153" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>2257</v>
       </c>
@@ -6252,10 +6270,10 @@
         <v>2958465</v>
       </c>
       <c r="I154" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>2257</v>
       </c>
@@ -6281,10 +6299,10 @@
         <v>2958465</v>
       </c>
       <c r="I155" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>2257</v>
       </c>
@@ -6310,10 +6328,10 @@
         <v>2958465</v>
       </c>
       <c r="I156" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>2257</v>
       </c>
@@ -6339,10 +6357,10 @@
         <v>2958465</v>
       </c>
       <c r="I157" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>2257</v>
       </c>
@@ -6368,10 +6386,10 @@
         <v>2958465</v>
       </c>
       <c r="I158" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>2257</v>
       </c>
@@ -6397,10 +6415,10 @@
         <v>2958465</v>
       </c>
       <c r="I159" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>2257</v>
       </c>
@@ -6426,10 +6444,10 @@
         <v>2958465</v>
       </c>
       <c r="I160" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>2257</v>
       </c>
@@ -6455,10 +6473,10 @@
         <v>2958465</v>
       </c>
       <c r="I161" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>2257</v>
       </c>
@@ -6484,10 +6502,10 @@
         <v>2958465</v>
       </c>
       <c r="I162" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>2257</v>
       </c>
@@ -6513,10 +6531,10 @@
         <v>2958465</v>
       </c>
       <c r="I163" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>2257</v>
       </c>
@@ -6542,10 +6560,10 @@
         <v>2958465</v>
       </c>
       <c r="I164" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>2204</v>
       </c>
@@ -6571,10 +6589,10 @@
         <v>2958465</v>
       </c>
       <c r="I165" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>2204</v>
       </c>
@@ -6600,10 +6618,10 @@
         <v>2958465</v>
       </c>
       <c r="I166" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>1571</v>
       </c>
@@ -6629,10 +6647,10 @@
         <v>2958465</v>
       </c>
       <c r="I167" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>1571</v>
       </c>
@@ -6658,10 +6676,10 @@
         <v>2958465</v>
       </c>
       <c r="I168" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>1571</v>
       </c>
@@ -6687,10 +6705,10 @@
         <v>2958465</v>
       </c>
       <c r="I169" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>1571</v>
       </c>
@@ -6716,10 +6734,10 @@
         <v>2958465</v>
       </c>
       <c r="I170" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>1571</v>
       </c>
@@ -6745,10 +6763,10 @@
         <v>2958465</v>
       </c>
       <c r="I171" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>1571</v>
       </c>
@@ -6774,10 +6792,10 @@
         <v>2958465</v>
       </c>
       <c r="I172" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>1571</v>
       </c>
@@ -6803,10 +6821,10 @@
         <v>2958465</v>
       </c>
       <c r="I173" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>1571</v>
       </c>
@@ -6832,10 +6850,10 @@
         <v>2958465</v>
       </c>
       <c r="I174" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>1571</v>
       </c>
@@ -6861,10 +6879,10 @@
         <v>2958465</v>
       </c>
       <c r="I175" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>1571</v>
       </c>
@@ -6890,10 +6908,10 @@
         <v>2958465</v>
       </c>
       <c r="I176" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>1571</v>
       </c>
@@ -6919,10 +6937,10 @@
         <v>2958465</v>
       </c>
       <c r="I177" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>1571</v>
       </c>
@@ -6948,10 +6966,10 @@
         <v>2958465</v>
       </c>
       <c r="I178" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>1571</v>
       </c>
@@ -6977,10 +6995,10 @@
         <v>2958465</v>
       </c>
       <c r="I179" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>1571</v>
       </c>
@@ -7006,10 +7024,10 @@
         <v>2958465</v>
       </c>
       <c r="I180" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>1571</v>
       </c>
@@ -7035,10 +7053,10 @@
         <v>2958465</v>
       </c>
       <c r="I181" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>1571</v>
       </c>
@@ -7064,10 +7082,10 @@
         <v>2958465</v>
       </c>
       <c r="I182" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>1571</v>
       </c>
@@ -7093,10 +7111,10 @@
         <v>2958465</v>
       </c>
       <c r="I183" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>1571</v>
       </c>
@@ -7122,10 +7140,10 @@
         <v>2958465</v>
       </c>
       <c r="I184" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>1571</v>
       </c>
@@ -7151,10 +7169,10 @@
         <v>2958465</v>
       </c>
       <c r="I185" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>1571</v>
       </c>
@@ -7180,10 +7198,10 @@
         <v>2958465</v>
       </c>
       <c r="I186" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>1571</v>
       </c>
@@ -7209,10 +7227,10 @@
         <v>2958465</v>
       </c>
       <c r="I187" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>1571</v>
       </c>
@@ -7238,10 +7256,10 @@
         <v>2958465</v>
       </c>
       <c r="I188" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>1571</v>
       </c>
@@ -7267,10 +7285,10 @@
         <v>2958465</v>
       </c>
       <c r="I189" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>1571</v>
       </c>
@@ -7296,10 +7314,10 @@
         <v>2958465</v>
       </c>
       <c r="I190" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>1571</v>
       </c>
@@ -7325,10 +7343,10 @@
         <v>2958465</v>
       </c>
       <c r="I191" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>1571</v>
       </c>
@@ -7354,10 +7372,10 @@
         <v>2958465</v>
       </c>
       <c r="I192" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>1571</v>
       </c>
@@ -7383,10 +7401,10 @@
         <v>2958465</v>
       </c>
       <c r="I193" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>1571</v>
       </c>
@@ -7412,10 +7430,10 @@
         <v>2958465</v>
       </c>
       <c r="I194" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>1629</v>
       </c>
@@ -7441,10 +7459,10 @@
         <v>2958465</v>
       </c>
       <c r="I195" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>1629</v>
       </c>
@@ -7470,10 +7488,10 @@
         <v>2958465</v>
       </c>
       <c r="I196" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>1629</v>
       </c>
@@ -7499,10 +7517,10 @@
         <v>2958465</v>
       </c>
       <c r="I197" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>1629</v>
       </c>
@@ -7528,10 +7546,10 @@
         <v>2958465</v>
       </c>
       <c r="I198" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>1629</v>
       </c>
@@ -7557,10 +7575,10 @@
         <v>2958465</v>
       </c>
       <c r="I199" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>1629</v>
       </c>
@@ -7586,10 +7604,10 @@
         <v>2958465</v>
       </c>
       <c r="I200" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>1629</v>
       </c>
@@ -7615,10 +7633,10 @@
         <v>2958465</v>
       </c>
       <c r="I201" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>1809</v>
       </c>
@@ -7644,10 +7662,10 @@
         <v>2958465</v>
       </c>
       <c r="I202" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>1809</v>
       </c>
@@ -7673,10 +7691,10 @@
         <v>2958465</v>
       </c>
       <c r="I203" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>1809</v>
       </c>
@@ -7702,10 +7720,10 @@
         <v>2958465</v>
       </c>
       <c r="I204" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>1809</v>
       </c>
@@ -7731,10 +7749,10 @@
         <v>2958465</v>
       </c>
       <c r="I205" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>1809</v>
       </c>
@@ -7760,10 +7778,10 @@
         <v>2958465</v>
       </c>
       <c r="I206" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>1809</v>
       </c>
@@ -7789,10 +7807,10 @@
         <v>2958465</v>
       </c>
       <c r="I207" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>1809</v>
       </c>
@@ -7818,10 +7836,10 @@
         <v>2958465</v>
       </c>
       <c r="I208" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.3">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>1809</v>
       </c>
@@ -7847,10 +7865,10 @@
         <v>2958465</v>
       </c>
       <c r="I209" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.3">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>1809</v>
       </c>
@@ -7876,10 +7894,10 @@
         <v>2958465</v>
       </c>
       <c r="I210" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.3">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>1809</v>
       </c>
@@ -7905,10 +7923,10 @@
         <v>2958465</v>
       </c>
       <c r="I211" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.3">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>1809</v>
       </c>
@@ -7934,10 +7952,10 @@
         <v>2958465</v>
       </c>
       <c r="I212" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.3">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>1809</v>
       </c>
@@ -7963,10 +7981,10 @@
         <v>2958465</v>
       </c>
       <c r="I213" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>1228</v>
       </c>
@@ -7992,10 +8010,10 @@
         <v>2958465</v>
       </c>
       <c r="I214" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.3">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>1228</v>
       </c>
@@ -8021,10 +8039,10 @@
         <v>2958465</v>
       </c>
       <c r="I215" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.3">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>1745</v>
       </c>
@@ -8050,10 +8068,10 @@
         <v>2958465</v>
       </c>
       <c r="I216" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.3">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>1745</v>
       </c>
@@ -8079,10 +8097,10 @@
         <v>2958465</v>
       </c>
       <c r="I217" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.3">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>1745</v>
       </c>
@@ -8108,10 +8126,10 @@
         <v>2958465</v>
       </c>
       <c r="I218" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.3">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>1745</v>
       </c>
@@ -8137,10 +8155,10 @@
         <v>2958465</v>
       </c>
       <c r="I219" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.3">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>1745</v>
       </c>
@@ -8166,10 +8184,10 @@
         <v>2958465</v>
       </c>
       <c r="I220" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.3">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>1745</v>
       </c>
@@ -8195,10 +8213,10 @@
         <v>2958465</v>
       </c>
       <c r="I221" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.3">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>1745</v>
       </c>
@@ -8224,10 +8242,10 @@
         <v>2958465</v>
       </c>
       <c r="I222" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.3">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>1745</v>
       </c>
@@ -8253,10 +8271,10 @@
         <v>2958465</v>
       </c>
       <c r="I223" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.3">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>1745</v>
       </c>
@@ -8282,10 +8300,10 @@
         <v>2958465</v>
       </c>
       <c r="I224" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.3">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>1745</v>
       </c>
@@ -8311,10 +8329,10 @@
         <v>2958465</v>
       </c>
       <c r="I225" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.3">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>1745</v>
       </c>
@@ -8340,10 +8358,10 @@
         <v>2958465</v>
       </c>
       <c r="I226" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>1745</v>
       </c>
@@ -8369,10 +8387,10 @@
         <v>2958465</v>
       </c>
       <c r="I227" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>1745</v>
       </c>
@@ -8398,10 +8416,10 @@
         <v>2958465</v>
       </c>
       <c r="I228" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.3">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>1745</v>
       </c>
@@ -8427,10 +8445,10 @@
         <v>2958465</v>
       </c>
       <c r="I229" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>1745</v>
       </c>
@@ -8456,10 +8474,10 @@
         <v>2958465</v>
       </c>
       <c r="I230" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.3">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>1745</v>
       </c>
@@ -8485,10 +8503,10 @@
         <v>2958465</v>
       </c>
       <c r="I231" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.3">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>1745</v>
       </c>
@@ -8514,10 +8532,10 @@
         <v>2958465</v>
       </c>
       <c r="I232" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.3">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>1745</v>
       </c>
@@ -8543,10 +8561,10 @@
         <v>2958465</v>
       </c>
       <c r="I233" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.3">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>1745</v>
       </c>
@@ -8572,10 +8590,10 @@
         <v>2958465</v>
       </c>
       <c r="I234" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.3">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>1745</v>
       </c>
@@ -8601,10 +8619,10 @@
         <v>2958465</v>
       </c>
       <c r="I235" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.3">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>1745</v>
       </c>
@@ -8630,10 +8648,10 @@
         <v>2958465</v>
       </c>
       <c r="I236" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.3">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>1745</v>
       </c>
@@ -8659,10 +8677,10 @@
         <v>2958465</v>
       </c>
       <c r="I237" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.3">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>1745</v>
       </c>
@@ -8688,10 +8706,10 @@
         <v>2958465</v>
       </c>
       <c r="I238" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.3">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>1745</v>
       </c>
@@ -8717,10 +8735,10 @@
         <v>2958465</v>
       </c>
       <c r="I239" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.3">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>1745</v>
       </c>
@@ -8746,10 +8764,10 @@
         <v>2958465</v>
       </c>
       <c r="I240" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.3">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>1230</v>
       </c>
@@ -8775,10 +8793,10 @@
         <v>2958465</v>
       </c>
       <c r="I241" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.3">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>2207</v>
       </c>
@@ -8804,10 +8822,10 @@
         <v>2958465</v>
       </c>
       <c r="I242" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.3">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>2207</v>
       </c>
@@ -8833,10 +8851,10 @@
         <v>2958465</v>
       </c>
       <c r="I243" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.3">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>2207</v>
       </c>
@@ -8862,10 +8880,10 @@
         <v>2958465</v>
       </c>
       <c r="I244" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.3">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>2207</v>
       </c>
@@ -8891,10 +8909,10 @@
         <v>2958465</v>
       </c>
       <c r="I245" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.3">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>2126</v>
       </c>
@@ -8920,10 +8938,10 @@
         <v>2958465</v>
       </c>
       <c r="I246" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.3">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="247" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>2126</v>
       </c>
@@ -8949,10 +8967,10 @@
         <v>2958465</v>
       </c>
       <c r="I247" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.3">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="248" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>2126</v>
       </c>
@@ -8978,10 +8996,10 @@
         <v>2958465</v>
       </c>
       <c r="I248" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="249" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>2244</v>
       </c>
@@ -9007,10 +9025,10 @@
         <v>2958465</v>
       </c>
       <c r="I249" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.3">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="250" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>2244</v>
       </c>
@@ -9036,10 +9054,10 @@
         <v>2958465</v>
       </c>
       <c r="I250" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.3">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>2244</v>
       </c>
@@ -9065,10 +9083,10 @@
         <v>2958465</v>
       </c>
       <c r="I251" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.3">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="252" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>2244</v>
       </c>
@@ -9094,10 +9112,10 @@
         <v>2958465</v>
       </c>
       <c r="I252" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.3">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>2244</v>
       </c>
@@ -9123,10 +9141,10 @@
         <v>2958465</v>
       </c>
       <c r="I253" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.3">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="254" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>1950</v>
       </c>
@@ -9152,10 +9170,10 @@
         <v>2958465</v>
       </c>
       <c r="I254" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.3">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>1950</v>
       </c>
@@ -9181,10 +9199,10 @@
         <v>2958465</v>
       </c>
       <c r="I255" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.3">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="256" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>2255</v>
       </c>
@@ -9210,10 +9228,10 @@
         <v>2958465</v>
       </c>
       <c r="I256" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.3">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>2250</v>
       </c>
@@ -9239,10 +9257,10 @@
         <v>2958465</v>
       </c>
       <c r="I257" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.3">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>2250</v>
       </c>
@@ -9268,10 +9286,10 @@
         <v>2958465</v>
       </c>
       <c r="I258" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.3">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>2250</v>
       </c>
@@ -9297,10 +9315,10 @@
         <v>2958465</v>
       </c>
       <c r="I259" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.3">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>2250</v>
       </c>
@@ -9326,10 +9344,10 @@
         <v>2958465</v>
       </c>
       <c r="I260" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.3">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>2250</v>
       </c>
@@ -9355,10 +9373,10 @@
         <v>2958465</v>
       </c>
       <c r="I261" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.3">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>2250</v>
       </c>
@@ -9384,10 +9402,17 @@
         <v>2958465</v>
       </c>
       <c r="I262" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I262" xr:uid="{9AECB136-8215-429B-82E5-8A6B6A669FFB}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="2258"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H262">
     <sortCondition ref="A2:A262"/>
     <sortCondition ref="B2:B262"/>
@@ -9399,12 +9424,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="MetaDocumentWS" ma:contentTypeID="0x01010002328573F07347D9A7800BDA19699CC200DE8F1DF1BF4211488DA32D5AC68DFB95" ma:contentTypeVersion="0" ma:contentTypeDescription="Metadata Content Type(Workshare)" ma:contentTypeScope="" ma:versionID="ea2efc4932be20cf5e8fe2ec0517f4d4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b6142cc285753f069fe6237cbe592e30">
     <xsd:element name="properties">
@@ -9518,16 +9552,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9975CE17-A2BF-4108-83DD-AD872CF67E1E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{034CDF24-425D-4892-AB7F-AACD3A1CB9F3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -9536,7 +9569,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D297E724-C9ED-40B8-8790-2B8BEFF24B33}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9550,12 +9583,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9975CE17-A2BF-4108-83DD-AD872CF67E1E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/existing/판매중_상품구성_사업방법서_매핑.xlsx
+++ b/data/existing/판매중_상품구성_사업방법서_매핑.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\claudecsw\ruleautomatker\data\existing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B446EF73-745F-4799-BCEC-BE4908B534A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04C39FC8-0191-4F05-8551-FD0A548C4423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="51480" yWindow="30" windowWidth="51840" windowHeight="21120" xr2:uid="{364CA86F-2012-40A9-A884-5853FC3C1200}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="보종코드_상품코드_매핑" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">보종코드_상품코드_매핑!$A$1:$I$262</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">보종코드_상품코드_매핑!$A$1:$N$262</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1784,13 +1784,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AECB136-8215-429B-82E5-8A6B6A669FFB}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:N262"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="73.875" customWidth="1"/>
+    <col min="3" max="3" width="131.875" customWidth="1"/>
     <col min="4" max="4" width="12.625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="100.375" customWidth="1"/>
@@ -1829,7 +1828,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2061</v>
       </c>
@@ -1858,7 +1857,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2061</v>
       </c>
@@ -1887,7 +1886,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1772</v>
       </c>
@@ -1916,7 +1915,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1772</v>
       </c>
@@ -1945,7 +1944,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1772</v>
       </c>
@@ -1974,7 +1973,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1772</v>
       </c>
@@ -2003,7 +2002,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1726</v>
       </c>
@@ -2032,7 +2031,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1726</v>
       </c>
@@ -2061,7 +2060,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1726</v>
       </c>
@@ -2090,7 +2089,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1726</v>
       </c>
@@ -2119,7 +2118,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>1764</v>
       </c>
@@ -2148,7 +2147,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1764</v>
       </c>
@@ -2177,7 +2176,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1764</v>
       </c>
@@ -2206,7 +2205,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1764</v>
       </c>
@@ -2235,7 +2234,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2170</v>
       </c>
@@ -2264,7 +2263,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2170</v>
       </c>
@@ -2293,7 +2292,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2170</v>
       </c>
@@ -2322,7 +2321,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2246</v>
       </c>
@@ -2351,7 +2350,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2246</v>
       </c>
@@ -2380,7 +2379,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2246</v>
       </c>
@@ -2409,7 +2408,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2246</v>
       </c>
@@ -2438,7 +2437,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2246</v>
       </c>
@@ -2467,7 +2466,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>2246</v>
       </c>
@@ -2496,7 +2495,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>2246</v>
       </c>
@@ -2525,7 +2524,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>2246</v>
       </c>
@@ -2554,7 +2553,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>2246</v>
       </c>
@@ -2583,7 +2582,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>2253</v>
       </c>
@@ -2612,7 +2611,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>2170</v>
       </c>
@@ -2641,7 +2640,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>2170</v>
       </c>
@@ -2670,7 +2669,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>2209</v>
       </c>
@@ -2699,7 +2698,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>2209</v>
       </c>
@@ -2728,7 +2727,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>2209</v>
       </c>
@@ -2757,7 +2756,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>2209</v>
       </c>
@@ -2786,7 +2785,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>2209</v>
       </c>
@@ -2815,7 +2814,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>2209</v>
       </c>
@@ -2844,7 +2843,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>2209</v>
       </c>
@@ -2873,7 +2872,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>2209</v>
       </c>
@@ -2902,7 +2901,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>2248</v>
       </c>
@@ -2931,7 +2930,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>1796</v>
       </c>
@@ -2960,7 +2959,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>1833</v>
       </c>
@@ -2989,7 +2988,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>1833</v>
       </c>
@@ -3018,7 +3017,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>2254</v>
       </c>
@@ -3047,7 +3046,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>2210</v>
       </c>
@@ -3076,7 +3075,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>2210</v>
       </c>
@@ -3105,7 +3104,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>2210</v>
       </c>
@@ -3134,7 +3133,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>2210</v>
       </c>
@@ -3163,7 +3162,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>2249</v>
       </c>
@@ -3192,7 +3191,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>2249</v>
       </c>
@@ -3221,7 +3220,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>2243</v>
       </c>
@@ -3250,7 +3249,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>2243</v>
       </c>
@@ -3279,7 +3278,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>2130</v>
       </c>
@@ -3308,7 +3307,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>2130</v>
       </c>
@@ -3337,7 +3336,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>2205</v>
       </c>
@@ -3366,7 +3365,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>2205</v>
       </c>
@@ -3395,7 +3394,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>1976</v>
       </c>
@@ -3424,7 +3423,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>1976</v>
       </c>
@@ -3453,7 +3452,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>1976</v>
       </c>
@@ -3482,7 +3481,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>1976</v>
       </c>
@@ -3511,7 +3510,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>2208</v>
       </c>
@@ -3540,7 +3539,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>2208</v>
       </c>
@@ -3569,7 +3568,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>2256</v>
       </c>
@@ -3598,7 +3597,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>2251</v>
       </c>
@@ -3627,7 +3626,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>2251</v>
       </c>
@@ -3656,7 +3655,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>2251</v>
       </c>
@@ -3685,7 +3684,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>2242</v>
       </c>
@@ -3714,7 +3713,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>2242</v>
       </c>
@@ -3743,7 +3742,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>2242</v>
       </c>
@@ -3772,7 +3771,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>2242</v>
       </c>
@@ -3801,7 +3800,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>1983</v>
       </c>
@@ -3830,7 +3829,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>1983</v>
       </c>
@@ -3859,7 +3858,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>1982</v>
       </c>
@@ -3888,7 +3887,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>1982</v>
       </c>
@@ -3917,7 +3916,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>1982</v>
       </c>
@@ -3946,7 +3945,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>1982</v>
       </c>
@@ -3975,7 +3974,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>1984</v>
       </c>
@@ -4004,7 +4003,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>1984</v>
       </c>
@@ -4033,7 +4032,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>1984</v>
       </c>
@@ -4062,7 +4061,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>1984</v>
       </c>
@@ -4091,7 +4090,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>1984</v>
       </c>
@@ -4120,7 +4119,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>1984</v>
       </c>
@@ -4149,7 +4148,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>1984</v>
       </c>
@@ -4178,7 +4177,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>1984</v>
       </c>
@@ -4207,7 +4206,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>1985</v>
       </c>
@@ -4236,7 +4235,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>1985</v>
       </c>
@@ -4265,7 +4264,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>1985</v>
       </c>
@@ -4294,7 +4293,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>1985</v>
       </c>
@@ -4323,7 +4322,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>1986</v>
       </c>
@@ -4352,7 +4351,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>1986</v>
       </c>
@@ -4381,7 +4380,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>1224</v>
       </c>
@@ -4410,7 +4409,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>1224</v>
       </c>
@@ -4439,7 +4438,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>1808</v>
       </c>
@@ -4468,7 +4467,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>1808</v>
       </c>
@@ -4497,7 +4496,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>1946</v>
       </c>
@@ -4526,7 +4525,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>1946</v>
       </c>
@@ -4555,7 +4554,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>2259</v>
       </c>
@@ -4584,7 +4583,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>2259</v>
       </c>
@@ -4613,7 +4612,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>2259</v>
       </c>
@@ -4642,7 +4641,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>2259</v>
       </c>
@@ -4671,7 +4670,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>2259</v>
       </c>
@@ -4700,7 +4699,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>2259</v>
       </c>
@@ -4729,7 +4728,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>2259</v>
       </c>
@@ -4758,7 +4757,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>2259</v>
       </c>
@@ -4787,7 +4786,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>2259</v>
       </c>
@@ -4816,7 +4815,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>2259</v>
       </c>
@@ -4845,7 +4844,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>2259</v>
       </c>
@@ -4874,7 +4873,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>2259</v>
       </c>
@@ -4903,7 +4902,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>2259</v>
       </c>
@@ -4932,7 +4931,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>2259</v>
       </c>
@@ -4961,7 +4960,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>2259</v>
       </c>
@@ -4990,7 +4989,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>2259</v>
       </c>
@@ -5019,7 +5018,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>2259</v>
       </c>
@@ -5048,7 +5047,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>2259</v>
       </c>
@@ -5077,7 +5076,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>2259</v>
       </c>
@@ -5106,7 +5105,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>2259</v>
       </c>
@@ -5135,7 +5134,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>2259</v>
       </c>
@@ -5164,7 +5163,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>2259</v>
       </c>
@@ -5193,7 +5192,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>2126</v>
       </c>
@@ -5222,7 +5221,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>2126</v>
       </c>
@@ -5251,7 +5250,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>2126</v>
       </c>
@@ -5280,7 +5279,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>2129</v>
       </c>
@@ -5309,7 +5308,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>2129</v>
       </c>
@@ -5338,7 +5337,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>2129</v>
       </c>
@@ -5367,7 +5366,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>2129</v>
       </c>
@@ -5396,7 +5395,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>2236</v>
       </c>
@@ -5425,7 +5424,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>2236</v>
       </c>
@@ -5454,7 +5453,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>2236</v>
       </c>
@@ -5483,7 +5482,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>2236</v>
       </c>
@@ -5512,7 +5511,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="129" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>1758</v>
       </c>
@@ -5541,7 +5540,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="130" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>1758</v>
       </c>
@@ -5570,7 +5569,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="131" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>1758</v>
       </c>
@@ -5599,7 +5598,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="132" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>1758</v>
       </c>
@@ -5628,7 +5627,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="133" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>1758</v>
       </c>
@@ -5657,7 +5656,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="134" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>2042</v>
       </c>
@@ -5686,7 +5685,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="135" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>2042</v>
       </c>
@@ -5715,7 +5714,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="136" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>2042</v>
       </c>
@@ -5744,7 +5743,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="137" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>2042</v>
       </c>
@@ -5773,7 +5772,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="138" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>2042</v>
       </c>
@@ -6186,7 +6185,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>2257</v>
       </c>
@@ -6215,7 +6214,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>2257</v>
       </c>
@@ -6244,7 +6243,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>2257</v>
       </c>
@@ -6273,7 +6272,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>2257</v>
       </c>
@@ -6302,7 +6301,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>2257</v>
       </c>
@@ -6331,7 +6330,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>2257</v>
       </c>
@@ -6360,7 +6359,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>2257</v>
       </c>
@@ -6389,7 +6388,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>2257</v>
       </c>
@@ -6418,7 +6417,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>2257</v>
       </c>
@@ -6447,7 +6446,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>2257</v>
       </c>
@@ -6476,7 +6475,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>2257</v>
       </c>
@@ -6505,7 +6504,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>2257</v>
       </c>
@@ -6534,7 +6533,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>2257</v>
       </c>
@@ -6563,7 +6562,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>2204</v>
       </c>
@@ -6592,7 +6591,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>2204</v>
       </c>
@@ -6621,7 +6620,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>1571</v>
       </c>
@@ -6650,7 +6649,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>1571</v>
       </c>
@@ -6679,7 +6678,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>1571</v>
       </c>
@@ -6708,7 +6707,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>1571</v>
       </c>
@@ -6737,7 +6736,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>1571</v>
       </c>
@@ -6766,7 +6765,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>1571</v>
       </c>
@@ -6795,7 +6794,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>1571</v>
       </c>
@@ -6824,7 +6823,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>1571</v>
       </c>
@@ -6853,7 +6852,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>1571</v>
       </c>
@@ -6882,7 +6881,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>1571</v>
       </c>
@@ -6911,7 +6910,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>1571</v>
       </c>
@@ -6940,7 +6939,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>1571</v>
       </c>
@@ -6969,7 +6968,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>1571</v>
       </c>
@@ -6998,7 +6997,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>1571</v>
       </c>
@@ -7027,7 +7026,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>1571</v>
       </c>
@@ -7056,7 +7055,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="182" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>1571</v>
       </c>
@@ -7085,7 +7084,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>1571</v>
       </c>
@@ -7114,7 +7113,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="184" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>1571</v>
       </c>
@@ -7143,7 +7142,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>1571</v>
       </c>
@@ -7172,7 +7171,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>1571</v>
       </c>
@@ -7201,7 +7200,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>1571</v>
       </c>
@@ -7230,7 +7229,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>1571</v>
       </c>
@@ -7259,7 +7258,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>1571</v>
       </c>
@@ -7288,7 +7287,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>1571</v>
       </c>
@@ -7317,7 +7316,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>1571</v>
       </c>
@@ -7346,7 +7345,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="192" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>1571</v>
       </c>
@@ -7375,7 +7374,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>1571</v>
       </c>
@@ -7404,7 +7403,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>1571</v>
       </c>
@@ -7433,7 +7432,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>1629</v>
       </c>
@@ -7462,7 +7461,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>1629</v>
       </c>
@@ -7491,7 +7490,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>1629</v>
       </c>
@@ -7520,7 +7519,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>1629</v>
       </c>
@@ -7549,7 +7548,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>1629</v>
       </c>
@@ -7578,7 +7577,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>1629</v>
       </c>
@@ -7607,7 +7606,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>1629</v>
       </c>
@@ -7636,7 +7635,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>1809</v>
       </c>
@@ -7665,7 +7664,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>1809</v>
       </c>
@@ -7694,7 +7693,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>1809</v>
       </c>
@@ -7723,7 +7722,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>1809</v>
       </c>
@@ -7752,7 +7751,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>1809</v>
       </c>
@@ -7781,7 +7780,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>1809</v>
       </c>
@@ -7810,7 +7809,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>1809</v>
       </c>
@@ -7839,7 +7838,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>1809</v>
       </c>
@@ -7868,7 +7867,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>1809</v>
       </c>
@@ -7897,7 +7896,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>1809</v>
       </c>
@@ -7926,7 +7925,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>1809</v>
       </c>
@@ -7955,7 +7954,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>1809</v>
       </c>
@@ -7984,7 +7983,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>1228</v>
       </c>
@@ -8013,7 +8012,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>1228</v>
       </c>
@@ -8042,7 +8041,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>1745</v>
       </c>
@@ -8071,7 +8070,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>1745</v>
       </c>
@@ -8100,7 +8099,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>1745</v>
       </c>
@@ -8129,7 +8128,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>1745</v>
       </c>
@@ -8158,7 +8157,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>1745</v>
       </c>
@@ -8187,7 +8186,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>1745</v>
       </c>
@@ -8216,7 +8215,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>1745</v>
       </c>
@@ -8245,7 +8244,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>1745</v>
       </c>
@@ -8274,7 +8273,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>1745</v>
       </c>
@@ -8303,7 +8302,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>1745</v>
       </c>
@@ -8332,7 +8331,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>1745</v>
       </c>
@@ -8361,7 +8360,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>1745</v>
       </c>
@@ -8390,7 +8389,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>1745</v>
       </c>
@@ -8419,7 +8418,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>1745</v>
       </c>
@@ -8448,7 +8447,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>1745</v>
       </c>
@@ -8477,7 +8476,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>1745</v>
       </c>
@@ -8506,7 +8505,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>1745</v>
       </c>
@@ -8535,7 +8534,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>1745</v>
       </c>
@@ -8564,7 +8563,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>1745</v>
       </c>
@@ -8593,7 +8592,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>1745</v>
       </c>
@@ -8622,7 +8621,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>1745</v>
       </c>
@@ -8651,7 +8650,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>1745</v>
       </c>
@@ -8680,7 +8679,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="238" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>1745</v>
       </c>
@@ -8709,7 +8708,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="239" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>1745</v>
       </c>
@@ -8738,7 +8737,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="240" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>1745</v>
       </c>
@@ -8767,7 +8766,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="241" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>1230</v>
       </c>
@@ -8796,7 +8795,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="242" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>2207</v>
       </c>
@@ -8825,7 +8824,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="243" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>2207</v>
       </c>
@@ -8854,7 +8853,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="244" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>2207</v>
       </c>
@@ -8883,7 +8882,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="245" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>2207</v>
       </c>
@@ -8912,7 +8911,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="246" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>2126</v>
       </c>
@@ -8941,7 +8940,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="247" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>2126</v>
       </c>
@@ -8970,7 +8969,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="248" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>2126</v>
       </c>
@@ -8999,7 +8998,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="249" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>2244</v>
       </c>
@@ -9028,7 +9027,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="250" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>2244</v>
       </c>
@@ -9057,7 +9056,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="251" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>2244</v>
       </c>
@@ -9086,7 +9085,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="252" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>2244</v>
       </c>
@@ -9115,7 +9114,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="253" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>2244</v>
       </c>
@@ -9144,7 +9143,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="254" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>1950</v>
       </c>
@@ -9173,7 +9172,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="255" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>1950</v>
       </c>
@@ -9202,7 +9201,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="256" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>2255</v>
       </c>
@@ -9231,7 +9230,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>2250</v>
       </c>
@@ -9260,7 +9259,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>2250</v>
       </c>
@@ -9289,7 +9288,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>2250</v>
       </c>
@@ -9318,7 +9317,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>2250</v>
       </c>
@@ -9347,7 +9346,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>2250</v>
       </c>
@@ -9376,7 +9375,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>2250</v>
       </c>
@@ -9406,13 +9405,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I262" xr:uid="{9AECB136-8215-429B-82E5-8A6B6A669FFB}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="2258"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H262">
     <sortCondition ref="A2:A262"/>
     <sortCondition ref="B2:B262"/>
@@ -9424,18 +9416,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9553,18 +9545,18 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9975CE17-A2BF-4108-83DD-AD872CF67E1E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{034CDF24-425D-4892-AB7F-AACD3A1CB9F3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{034CDF24-425D-4892-AB7F-AACD3A1CB9F3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9975CE17-A2BF-4108-83DD-AD872CF67E1E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data/existing/판매중_상품구성_사업방법서_매핑.xlsx
+++ b/data/existing/판매중_상품구성_사업방법서_매핑.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\claudecsw\ruleautomatker\data\existing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04C39FC8-0191-4F05-8551-FD0A548C4423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33AE1D88-8639-48F9-B030-CB186CCCCC31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="51480" yWindow="30" windowWidth="51840" windowHeight="21120" xr2:uid="{364CA86F-2012-40A9-A884-5853FC3C1200}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="502">
   <si>
     <t>ISRN_KIND_DTCD</t>
   </si>
@@ -1412,6 +1412,145 @@
   <si>
     <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형)_사업방법서_20260201~.pdf</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>doc파일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>한화생명 e암보험(비갱신형) 무배당_사업방법서 v1(노랑).docx</t>
+  </si>
+  <si>
+    <t>한화생명 e연금저축보험 무배당_사업방법서 v1(노랑).docx</t>
+  </si>
+  <si>
+    <t>한화생명 e정기보험 무배당_사업방법서_v3(하늘).docx</t>
+  </si>
+  <si>
+    <t>한화생명 H 기업재해보장보험 무배당_사업방법서_v1(노랑).docx</t>
+  </si>
+  <si>
+    <t>한화생명 H간병보험 무배당 사업방법서_v1(노랑).docx</t>
+  </si>
+  <si>
+    <t>한화생명 H건강플러스보험 무배당 사업방법서_v6(청록).docx</t>
+  </si>
+  <si>
+    <t>한화생명 H당뇨보험 무배당_사업방법서_v1.2(초록).docx</t>
+  </si>
+  <si>
+    <t>한화생명 H종신보험 무배당 사업방법서_V2(초록).docx</t>
+  </si>
+  <si>
+    <t>한화생명 간편가입 Need AI 암보험 무배당 사업방법서_v2(연두).docx</t>
+  </si>
+  <si>
+    <t>한화생명 Wealth단체저축보험 무배당 사업방법서_v1(노랑).docx</t>
+  </si>
+  <si>
+    <t>한화생명 Wealth직장인연금보험 무배당 사업방법서_v2(초록).docx</t>
+  </si>
+  <si>
+    <t>한화생명 간편가입 H당뇨보험 무배당_사업방법서_v1.2(초록).docx</t>
+  </si>
+  <si>
+    <t>한화생명 간편가입 H종신보험 무배당 사업방법서_V3(하늘).docx</t>
+  </si>
+  <si>
+    <t>한화생명 간편가입 경영인H정기보험 무배당 사업방법서_v4(분홍).docx</t>
+  </si>
+  <si>
+    <t>한화생명 간편가입 상속H종신보험 무배당_사업방법서_v2.1(초록).docx</t>
+  </si>
+  <si>
+    <t>한화생명 간편가입 시그니처H암보험 무배당 사업방법서_v4(분홍).docx</t>
+  </si>
+  <si>
+    <t>한화생명 간편가입 실손의료비보장보험(갱신형) 무배당(재가입전용) 사업방법서_v3(파랑).docx</t>
+  </si>
+  <si>
+    <t>한화생명 간편가입 제로백H종신보험 무배당_사업방법서_v1(노랑).docx</t>
+  </si>
+  <si>
+    <t>한화생명 간편가입 포켓골절보험 무배당 사업방법서_v3(초록).docx</t>
+  </si>
+  <si>
+    <t>한화생명 간편가입 하나로H종신보험 무배당_사업방법서_v5.0(파랑).docx</t>
+  </si>
+  <si>
+    <t>한화생명 경영인H정기보험 무배당 사업방법서_v4(분홍).docx</t>
+  </si>
+  <si>
+    <t>한화생명 기본형 급여 실손의료비보장보험(갱신형) 무배당 사업방법서_v1(노랑).docx</t>
+  </si>
+  <si>
+    <t>한화생명 기본형 급여 실손의료비보장보험[계약전환·단체개인전환·개인중지재개용](갱신형) 무배당 사업방법서_v1(노랑).docx</t>
+  </si>
+  <si>
+    <t>한화생명 기업복지라이프플랜보험 무배당_사업방법서_v1(노랑).docx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>한화생명 노후실손의료비보장보험(갱신형) 무배당 사업방법서_v2(노랑).docx</t>
+  </si>
+  <si>
+    <t>한화생명 바로연금보험 무배당 사업방법서_v1(노랑).docx</t>
+  </si>
+  <si>
+    <t>한화생명 진심가득H보장보험 무배당 사업방법서_v2(연두).docx</t>
+  </si>
+  <si>
+    <t>한화생명 상속H종신보험 무배당_사업방법서_v2.1(초록).docx</t>
+  </si>
+  <si>
+    <t>한화생명 스마트V상해보험 무배당_20260201_사업방법서_v2(초록).docx</t>
+  </si>
+  <si>
+    <t>한화생명 스마트V연금보험 무배당 사업방법서_v2(초록).docx</t>
+  </si>
+  <si>
+    <t>한화생명 스마트하이브리드연금보험 무배당 사업방법서_v2(연두).docx</t>
+  </si>
+  <si>
+    <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 사업방법서_v6(올리브).docx</t>
+  </si>
+  <si>
+    <t>한화생명 시그니처 H통합건강보험 무배당 사업방법서_v6(올리브).docx</t>
+  </si>
+  <si>
+    <t>한화생명 시그니처H암보험 무배당 사업방법서_v4(분홍).docx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>한화생명 연금보험Enterprise 무배당 사업방법서_v1(노랑).docx</t>
+  </si>
+  <si>
+    <t>한화생명 연금저축 미래로기업복지연금보험_사업방법서_v1(노랑).docx</t>
+  </si>
+  <si>
+    <t>한화생명 스마트하이브리드연금보험 무배당 사업방법서_v2(연두).docx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>한화생명 연금저축 하이드림연금보험 사업방법서_v1(노랑).docx</t>
+  </si>
+  <si>
+    <t>한화생명 장애인전용 곰두리보장보험 무배당_사업방법서_v1(노랑).docx</t>
+  </si>
+  <si>
+    <t>한화생명 제로백H종신보험 무배당_사업방법서_v1(노랑).docx</t>
+  </si>
+  <si>
+    <t>한화생명 케어백간병플러스보험 무배당 사업방법서_v3(옥색음영).docx</t>
+  </si>
+  <si>
+    <t>한화생명 튼튼이 치아보험(갱신형) 무배당 사업방법서_v3(파랑).docx</t>
+  </si>
+  <si>
+    <t>한화생명 포켓골절보험 무배당 사업방법서_v2(노랑).docx</t>
+  </si>
+  <si>
+    <t>한화생명 하나로H종신보험 무배당_사업방법서_v5.0(파랑).docx</t>
   </si>
 </sst>
 </file>
@@ -1438,12 +1577,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1460,7 +1605,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1468,6 +1613,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1796,10 +1944,11 @@
     <col min="7" max="7" width="24" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="23.875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="59.5" customWidth="1"/>
+    <col min="10" max="10" width="86.125" customWidth="1"/>
     <col min="14" max="14" width="23.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1827,8 +1976,11 @@
       <c r="I1" t="s">
         <v>453</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J1" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2061</v>
       </c>
@@ -1856,8 +2008,11 @@
       <c r="I2" t="s">
         <v>403</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J2" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2061</v>
       </c>
@@ -1885,8 +2040,11 @@
       <c r="I3" t="s">
         <v>403</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J3" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1772</v>
       </c>
@@ -1914,8 +2072,11 @@
       <c r="I4" t="s">
         <v>404</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J4" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1772</v>
       </c>
@@ -1943,8 +2104,11 @@
       <c r="I5" t="s">
         <v>404</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J5" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1772</v>
       </c>
@@ -1972,8 +2136,11 @@
       <c r="I6" t="s">
         <v>404</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J6" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1772</v>
       </c>
@@ -2001,8 +2168,11 @@
       <c r="I7" t="s">
         <v>404</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J7" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1726</v>
       </c>
@@ -2030,8 +2200,11 @@
       <c r="I8" t="s">
         <v>405</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J8" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1726</v>
       </c>
@@ -2059,8 +2232,11 @@
       <c r="I9" t="s">
         <v>405</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J9" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1726</v>
       </c>
@@ -2088,8 +2264,11 @@
       <c r="I10" t="s">
         <v>405</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J10" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1726</v>
       </c>
@@ -2117,8 +2296,11 @@
       <c r="I11" t="s">
         <v>405</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J11" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>1764</v>
       </c>
@@ -2146,8 +2328,11 @@
       <c r="I12" t="s">
         <v>406</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J12" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1764</v>
       </c>
@@ -2175,8 +2360,11 @@
       <c r="I13" t="s">
         <v>406</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J13" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1764</v>
       </c>
@@ -2204,8 +2392,11 @@
       <c r="I14" t="s">
         <v>406</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J14" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1764</v>
       </c>
@@ -2233,8 +2424,11 @@
       <c r="I15" t="s">
         <v>406</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J15" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2170</v>
       </c>
@@ -2262,8 +2456,11 @@
       <c r="I16" t="s">
         <v>407</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J16" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2170</v>
       </c>
@@ -2291,8 +2488,11 @@
       <c r="I17" t="s">
         <v>407</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J17" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2170</v>
       </c>
@@ -2320,8 +2520,11 @@
       <c r="I18" t="s">
         <v>407</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J18" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2246</v>
       </c>
@@ -2349,8 +2552,11 @@
       <c r="I19" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J19" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2246</v>
       </c>
@@ -2378,8 +2584,11 @@
       <c r="I20" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J20" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2246</v>
       </c>
@@ -2407,8 +2616,11 @@
       <c r="I21" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J21" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2246</v>
       </c>
@@ -2436,8 +2648,11 @@
       <c r="I22" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J22" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2246</v>
       </c>
@@ -2465,8 +2680,11 @@
       <c r="I23" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J23" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>2246</v>
       </c>
@@ -2494,8 +2712,11 @@
       <c r="I24" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J24" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>2246</v>
       </c>
@@ -2523,8 +2744,11 @@
       <c r="I25" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J25" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>2246</v>
       </c>
@@ -2552,8 +2776,11 @@
       <c r="I26" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J26" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>2246</v>
       </c>
@@ -2581,8 +2808,11 @@
       <c r="I27" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J27" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>2253</v>
       </c>
@@ -2610,8 +2840,11 @@
       <c r="I28" t="s">
         <v>409</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J28" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>2170</v>
       </c>
@@ -2639,8 +2872,11 @@
       <c r="I29" t="s">
         <v>410</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J29" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>2170</v>
       </c>
@@ -2668,8 +2904,11 @@
       <c r="I30" t="s">
         <v>410</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J30" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>2209</v>
       </c>
@@ -2697,8 +2936,11 @@
       <c r="I31" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J31" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>2209</v>
       </c>
@@ -2726,8 +2968,11 @@
       <c r="I32" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J32" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>2209</v>
       </c>
@@ -2755,8 +3000,11 @@
       <c r="I33" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J33" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>2209</v>
       </c>
@@ -2784,8 +3032,11 @@
       <c r="I34" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J34" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>2209</v>
       </c>
@@ -2813,8 +3064,11 @@
       <c r="I35" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J35" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>2209</v>
       </c>
@@ -2842,8 +3096,11 @@
       <c r="I36" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J36" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>2209</v>
       </c>
@@ -2871,8 +3128,11 @@
       <c r="I37" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J37" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>2209</v>
       </c>
@@ -2900,8 +3160,11 @@
       <c r="I38" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J38" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>2248</v>
       </c>
@@ -2929,8 +3192,11 @@
       <c r="I39" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J39" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>1796</v>
       </c>
@@ -2958,8 +3224,11 @@
       <c r="I40" t="s">
         <v>412</v>
       </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J40" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>1833</v>
       </c>
@@ -2987,8 +3256,11 @@
       <c r="I41" t="s">
         <v>413</v>
       </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J41" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>1833</v>
       </c>
@@ -3016,8 +3288,11 @@
       <c r="I42" t="s">
         <v>413</v>
       </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J42" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>2254</v>
       </c>
@@ -3045,8 +3320,11 @@
       <c r="I43" t="s">
         <v>414</v>
       </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J43" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>2210</v>
       </c>
@@ -3074,8 +3352,11 @@
       <c r="I44" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J44" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>2210</v>
       </c>
@@ -3103,8 +3384,11 @@
       <c r="I45" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J45" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>2210</v>
       </c>
@@ -3132,8 +3416,11 @@
       <c r="I46" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J46" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>2210</v>
       </c>
@@ -3161,8 +3448,11 @@
       <c r="I47" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J47" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>2249</v>
       </c>
@@ -3190,8 +3480,11 @@
       <c r="I48" t="s">
         <v>416</v>
       </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J48" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>2249</v>
       </c>
@@ -3219,8 +3512,11 @@
       <c r="I49" t="s">
         <v>416</v>
       </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J49" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>2243</v>
       </c>
@@ -3248,8 +3544,11 @@
       <c r="I50" t="s">
         <v>417</v>
       </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J50" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>2243</v>
       </c>
@@ -3277,8 +3576,11 @@
       <c r="I51" t="s">
         <v>417</v>
       </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J51" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>2130</v>
       </c>
@@ -3306,8 +3608,11 @@
       <c r="I52" t="s">
         <v>418</v>
       </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J52" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>2130</v>
       </c>
@@ -3335,8 +3640,11 @@
       <c r="I53" t="s">
         <v>418</v>
       </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J53" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>2205</v>
       </c>
@@ -3364,8 +3672,11 @@
       <c r="I54" t="s">
         <v>419</v>
       </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J54" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>2205</v>
       </c>
@@ -3393,8 +3704,11 @@
       <c r="I55" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J55" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>1976</v>
       </c>
@@ -3422,8 +3736,11 @@
       <c r="I56" t="s">
         <v>421</v>
       </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J56" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>1976</v>
       </c>
@@ -3451,8 +3768,11 @@
       <c r="I57" t="s">
         <v>421</v>
       </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J57" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>1976</v>
       </c>
@@ -3480,8 +3800,11 @@
       <c r="I58" t="s">
         <v>421</v>
       </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J58" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>1976</v>
       </c>
@@ -3509,8 +3832,11 @@
       <c r="I59" t="s">
         <v>421</v>
       </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J59" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>2208</v>
       </c>
@@ -3538,8 +3864,11 @@
       <c r="I60" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J60" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>2208</v>
       </c>
@@ -3567,8 +3896,11 @@
       <c r="I61" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J61" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>2256</v>
       </c>
@@ -3596,8 +3928,11 @@
       <c r="I62" t="s">
         <v>423</v>
       </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J62" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>2251</v>
       </c>
@@ -3625,8 +3960,11 @@
       <c r="I63" t="s">
         <v>424</v>
       </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J63" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>2251</v>
       </c>
@@ -3654,8 +3992,11 @@
       <c r="I64" t="s">
         <v>424</v>
       </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J64" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>2251</v>
       </c>
@@ -3683,8 +4024,11 @@
       <c r="I65" t="s">
         <v>424</v>
       </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J65" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>2242</v>
       </c>
@@ -3712,8 +4056,11 @@
       <c r="I66" t="s">
         <v>425</v>
       </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J66" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>2242</v>
       </c>
@@ -3741,8 +4088,11 @@
       <c r="I67" t="s">
         <v>425</v>
       </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J67" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>2242</v>
       </c>
@@ -3770,8 +4120,11 @@
       <c r="I68" t="s">
         <v>425</v>
       </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J68" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>2242</v>
       </c>
@@ -3799,8 +4152,11 @@
       <c r="I69" t="s">
         <v>425</v>
       </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J69" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>1983</v>
       </c>
@@ -3828,8 +4184,11 @@
       <c r="I70" t="s">
         <v>426</v>
       </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J70" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>1983</v>
       </c>
@@ -3857,8 +4216,11 @@
       <c r="I71" t="s">
         <v>426</v>
       </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J71" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>1982</v>
       </c>
@@ -3886,8 +4248,11 @@
       <c r="I72" t="s">
         <v>427</v>
       </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J72" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>1982</v>
       </c>
@@ -3915,8 +4280,11 @@
       <c r="I73" t="s">
         <v>427</v>
       </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J73" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>1982</v>
       </c>
@@ -3944,8 +4312,11 @@
       <c r="I74" t="s">
         <v>427</v>
       </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J74" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>1982</v>
       </c>
@@ -3973,8 +4344,11 @@
       <c r="I75" t="s">
         <v>427</v>
       </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J75" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>1984</v>
       </c>
@@ -4002,8 +4376,11 @@
       <c r="I76" t="s">
         <v>428</v>
       </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J76" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>1984</v>
       </c>
@@ -4031,8 +4408,11 @@
       <c r="I77" t="s">
         <v>428</v>
       </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J77" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>1984</v>
       </c>
@@ -4060,8 +4440,11 @@
       <c r="I78" t="s">
         <v>428</v>
       </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J78" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>1984</v>
       </c>
@@ -4089,8 +4472,11 @@
       <c r="I79" t="s">
         <v>428</v>
       </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J79" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>1984</v>
       </c>
@@ -4118,8 +4504,11 @@
       <c r="I80" t="s">
         <v>428</v>
       </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J80" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>1984</v>
       </c>
@@ -4147,8 +4536,11 @@
       <c r="I81" t="s">
         <v>428</v>
       </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J81" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>1984</v>
       </c>
@@ -4176,8 +4568,11 @@
       <c r="I82" t="s">
         <v>428</v>
       </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J82" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>1984</v>
       </c>
@@ -4205,8 +4600,11 @@
       <c r="I83" t="s">
         <v>428</v>
       </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J83" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>1985</v>
       </c>
@@ -4234,8 +4632,11 @@
       <c r="I84" t="s">
         <v>428</v>
       </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J84" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>1985</v>
       </c>
@@ -4263,8 +4664,11 @@
       <c r="I85" t="s">
         <v>428</v>
       </c>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J85" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>1985</v>
       </c>
@@ -4292,8 +4696,11 @@
       <c r="I86" t="s">
         <v>428</v>
       </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J86" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>1985</v>
       </c>
@@ -4321,8 +4728,11 @@
       <c r="I87" t="s">
         <v>428</v>
       </c>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J87" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>1986</v>
       </c>
@@ -4350,8 +4760,11 @@
       <c r="I88" t="s">
         <v>428</v>
       </c>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J88" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>1986</v>
       </c>
@@ -4379,8 +4792,11 @@
       <c r="I89" t="s">
         <v>428</v>
       </c>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J89" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>1224</v>
       </c>
@@ -4408,8 +4824,11 @@
       <c r="I90" t="s">
         <v>429</v>
       </c>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J90" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>1224</v>
       </c>
@@ -4437,8 +4856,11 @@
       <c r="I91" t="s">
         <v>429</v>
       </c>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J91" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>1808</v>
       </c>
@@ -4466,8 +4888,11 @@
       <c r="I92" t="s">
         <v>430</v>
       </c>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J92" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>1808</v>
       </c>
@@ -4495,8 +4920,11 @@
       <c r="I93" t="s">
         <v>430</v>
       </c>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J93" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>1946</v>
       </c>
@@ -4524,8 +4952,11 @@
       <c r="I94" t="s">
         <v>430</v>
       </c>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J94" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>1946</v>
       </c>
@@ -4553,8 +4984,11 @@
       <c r="I95" t="s">
         <v>430</v>
       </c>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J95" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>2259</v>
       </c>
@@ -4582,8 +5016,11 @@
       <c r="I96" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J96" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>2259</v>
       </c>
@@ -4611,8 +5048,11 @@
       <c r="I97" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J97" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>2259</v>
       </c>
@@ -4640,8 +5080,11 @@
       <c r="I98" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J98" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>2259</v>
       </c>
@@ -4669,8 +5112,11 @@
       <c r="I99" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J99" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>2259</v>
       </c>
@@ -4698,8 +5144,11 @@
       <c r="I100" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J100" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>2259</v>
       </c>
@@ -4727,8 +5176,11 @@
       <c r="I101" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J101" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>2259</v>
       </c>
@@ -4756,8 +5208,11 @@
       <c r="I102" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J102" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>2259</v>
       </c>
@@ -4785,8 +5240,11 @@
       <c r="I103" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J103" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>2259</v>
       </c>
@@ -4814,8 +5272,11 @@
       <c r="I104" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J104" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>2259</v>
       </c>
@@ -4843,8 +5304,11 @@
       <c r="I105" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J105" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>2259</v>
       </c>
@@ -4872,8 +5336,11 @@
       <c r="I106" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J106" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>2259</v>
       </c>
@@ -4901,8 +5368,11 @@
       <c r="I107" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J107" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>2259</v>
       </c>
@@ -4930,8 +5400,11 @@
       <c r="I108" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J108" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>2259</v>
       </c>
@@ -4959,8 +5432,11 @@
       <c r="I109" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J109" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>2259</v>
       </c>
@@ -4988,8 +5464,11 @@
       <c r="I110" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J110" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>2259</v>
       </c>
@@ -5017,8 +5496,11 @@
       <c r="I111" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J111" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>2259</v>
       </c>
@@ -5046,8 +5528,11 @@
       <c r="I112" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J112" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>2259</v>
       </c>
@@ -5075,8 +5560,11 @@
       <c r="I113" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J113" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>2259</v>
       </c>
@@ -5104,8 +5592,11 @@
       <c r="I114" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J114" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>2259</v>
       </c>
@@ -5133,8 +5624,11 @@
       <c r="I115" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J115" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>2259</v>
       </c>
@@ -5162,8 +5656,11 @@
       <c r="I116" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J116" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>2259</v>
       </c>
@@ -5191,8 +5688,11 @@
       <c r="I117" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J117" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>2126</v>
       </c>
@@ -5220,8 +5720,11 @@
       <c r="I118" t="s">
         <v>432</v>
       </c>
-    </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J118" s="3" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>2126</v>
       </c>
@@ -5249,8 +5752,11 @@
       <c r="I119" t="s">
         <v>432</v>
       </c>
-    </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J119" s="3" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>2126</v>
       </c>
@@ -5278,8 +5784,11 @@
       <c r="I120" t="s">
         <v>432</v>
       </c>
-    </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J120" s="3" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>2129</v>
       </c>
@@ -5307,8 +5816,11 @@
       <c r="I121" t="s">
         <v>454</v>
       </c>
-    </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J121" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>2129</v>
       </c>
@@ -5336,8 +5848,11 @@
       <c r="I122" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J122" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>2129</v>
       </c>
@@ -5365,8 +5880,11 @@
       <c r="I123" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J123" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>2129</v>
       </c>
@@ -5394,8 +5912,11 @@
       <c r="I124" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J124" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>2236</v>
       </c>
@@ -5423,8 +5944,11 @@
       <c r="I125" t="s">
         <v>434</v>
       </c>
-    </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J125" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>2236</v>
       </c>
@@ -5452,8 +5976,11 @@
       <c r="I126" t="s">
         <v>434</v>
       </c>
-    </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J126" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>2236</v>
       </c>
@@ -5481,8 +6008,11 @@
       <c r="I127" t="s">
         <v>435</v>
       </c>
-    </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J127" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>2236</v>
       </c>
@@ -5509,6 +6039,9 @@
       </c>
       <c r="I128" t="s">
         <v>435</v>
+      </c>
+      <c r="J128" t="s">
+        <v>486</v>
       </c>
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.3">
@@ -5539,6 +6072,9 @@
       <c r="I129" t="s">
         <v>436</v>
       </c>
+      <c r="J129" t="s">
+        <v>487</v>
+      </c>
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A130">
@@ -5568,6 +6104,9 @@
       <c r="I130" t="s">
         <v>436</v>
       </c>
+      <c r="J130" t="s">
+        <v>487</v>
+      </c>
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A131">
@@ -5597,6 +6136,9 @@
       <c r="I131" t="s">
         <v>436</v>
       </c>
+      <c r="J131" t="s">
+        <v>487</v>
+      </c>
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A132">
@@ -5626,6 +6168,9 @@
       <c r="I132" t="s">
         <v>436</v>
       </c>
+      <c r="J132" t="s">
+        <v>487</v>
+      </c>
     </row>
     <row r="133" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A133">
@@ -5655,6 +6200,9 @@
       <c r="I133" t="s">
         <v>436</v>
       </c>
+      <c r="J133" t="s">
+        <v>487</v>
+      </c>
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A134">
@@ -5684,6 +6232,9 @@
       <c r="I134" t="s">
         <v>437</v>
       </c>
+      <c r="J134" t="s">
+        <v>488</v>
+      </c>
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A135">
@@ -5713,6 +6264,9 @@
       <c r="I135" t="s">
         <v>437</v>
       </c>
+      <c r="J135" t="s">
+        <v>488</v>
+      </c>
     </row>
     <row r="136" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A136">
@@ -5742,6 +6296,9 @@
       <c r="I136" t="s">
         <v>437</v>
       </c>
+      <c r="J136" t="s">
+        <v>488</v>
+      </c>
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A137">
@@ -5771,6 +6328,9 @@
       <c r="I137" t="s">
         <v>437</v>
       </c>
+      <c r="J137" t="s">
+        <v>488</v>
+      </c>
     </row>
     <row r="138" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A138">
@@ -5800,6 +6360,9 @@
       <c r="I138" t="s">
         <v>437</v>
       </c>
+      <c r="J138" t="s">
+        <v>488</v>
+      </c>
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A139">
@@ -5829,6 +6392,9 @@
       <c r="I139" t="s">
         <v>456</v>
       </c>
+      <c r="J139" t="s">
+        <v>489</v>
+      </c>
     </row>
     <row r="140" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A140">
@@ -5858,6 +6424,9 @@
       <c r="I140" t="s">
         <v>438</v>
       </c>
+      <c r="J140" t="s">
+        <v>489</v>
+      </c>
       <c r="M140">
         <f>IF(I139=N140,1,2)</f>
         <v>1</v>
@@ -5894,6 +6463,9 @@
       <c r="I141" t="s">
         <v>438</v>
       </c>
+      <c r="J141" t="s">
+        <v>489</v>
+      </c>
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A142">
@@ -5923,6 +6495,9 @@
       <c r="I142" t="s">
         <v>438</v>
       </c>
+      <c r="J142" t="s">
+        <v>489</v>
+      </c>
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A143">
@@ -5952,6 +6527,9 @@
       <c r="I143" t="s">
         <v>438</v>
       </c>
+      <c r="J143" t="s">
+        <v>489</v>
+      </c>
     </row>
     <row r="144" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A144">
@@ -5981,8 +6559,11 @@
       <c r="I144" t="s">
         <v>438</v>
       </c>
-    </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J144" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>2258</v>
       </c>
@@ -6010,8 +6591,11 @@
       <c r="I145" t="s">
         <v>438</v>
       </c>
-    </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J145" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>2258</v>
       </c>
@@ -6039,8 +6623,11 @@
       <c r="I146" t="s">
         <v>438</v>
       </c>
-    </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J146" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>2258</v>
       </c>
@@ -6068,8 +6655,11 @@
       <c r="I147" t="s">
         <v>438</v>
       </c>
-    </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J147" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>2258</v>
       </c>
@@ -6097,8 +6687,11 @@
       <c r="I148" t="s">
         <v>438</v>
       </c>
-    </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J148" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>2258</v>
       </c>
@@ -6126,8 +6719,11 @@
       <c r="I149" t="s">
         <v>438</v>
       </c>
-    </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J149" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>2258</v>
       </c>
@@ -6155,8 +6751,11 @@
       <c r="I150" t="s">
         <v>438</v>
       </c>
-    </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J150" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>2258</v>
       </c>
@@ -6184,8 +6783,11 @@
       <c r="I151" t="s">
         <v>438</v>
       </c>
-    </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J151" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>2257</v>
       </c>
@@ -6213,8 +6815,11 @@
       <c r="I152" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J152" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>2257</v>
       </c>
@@ -6242,8 +6847,11 @@
       <c r="I153" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J153" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>2257</v>
       </c>
@@ -6271,8 +6879,11 @@
       <c r="I154" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J154" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>2257</v>
       </c>
@@ -6300,8 +6911,11 @@
       <c r="I155" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J155" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>2257</v>
       </c>
@@ -6329,8 +6943,11 @@
       <c r="I156" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J156" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>2257</v>
       </c>
@@ -6358,8 +6975,11 @@
       <c r="I157" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J157" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>2257</v>
       </c>
@@ -6387,8 +7007,11 @@
       <c r="I158" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J158" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>2257</v>
       </c>
@@ -6416,8 +7039,11 @@
       <c r="I159" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J159" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>2257</v>
       </c>
@@ -6445,8 +7071,11 @@
       <c r="I160" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J160" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>2257</v>
       </c>
@@ -6474,8 +7103,11 @@
       <c r="I161" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J161" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>2257</v>
       </c>
@@ -6503,8 +7135,11 @@
       <c r="I162" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J162" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>2257</v>
       </c>
@@ -6532,8 +7167,11 @@
       <c r="I163" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J163" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>2257</v>
       </c>
@@ -6561,8 +7199,11 @@
       <c r="I164" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J164" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>2204</v>
       </c>
@@ -6590,8 +7231,11 @@
       <c r="I165" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J165" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>2204</v>
       </c>
@@ -6619,8 +7263,11 @@
       <c r="I166" t="s">
         <v>441</v>
       </c>
-    </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J166" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>1571</v>
       </c>
@@ -6648,8 +7295,11 @@
       <c r="I167" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J167" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>1571</v>
       </c>
@@ -6677,8 +7327,11 @@
       <c r="I168" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J168" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>1571</v>
       </c>
@@ -6706,8 +7359,11 @@
       <c r="I169" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J169" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>1571</v>
       </c>
@@ -6735,8 +7391,11 @@
       <c r="I170" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J170" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>1571</v>
       </c>
@@ -6764,8 +7423,11 @@
       <c r="I171" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J171" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>1571</v>
       </c>
@@ -6793,8 +7455,11 @@
       <c r="I172" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J172" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>1571</v>
       </c>
@@ -6822,8 +7487,11 @@
       <c r="I173" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J173" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>1571</v>
       </c>
@@ -6851,8 +7519,11 @@
       <c r="I174" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J174" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>1571</v>
       </c>
@@ -6880,8 +7551,11 @@
       <c r="I175" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J175" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>1571</v>
       </c>
@@ -6909,8 +7583,11 @@
       <c r="I176" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J176" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>1571</v>
       </c>
@@ -6938,8 +7615,11 @@
       <c r="I177" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J177" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>1571</v>
       </c>
@@ -6967,8 +7647,11 @@
       <c r="I178" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J178" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>1571</v>
       </c>
@@ -6996,8 +7679,11 @@
       <c r="I179" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J179" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="180" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>1571</v>
       </c>
@@ -7025,8 +7711,11 @@
       <c r="I180" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J180" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="181" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>1571</v>
       </c>
@@ -7054,8 +7743,11 @@
       <c r="I181" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J181" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="182" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>1571</v>
       </c>
@@ -7083,8 +7775,11 @@
       <c r="I182" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J182" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="183" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>1571</v>
       </c>
@@ -7112,8 +7807,11 @@
       <c r="I183" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J183" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="184" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>1571</v>
       </c>
@@ -7141,8 +7839,11 @@
       <c r="I184" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J184" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="185" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>1571</v>
       </c>
@@ -7170,8 +7871,11 @@
       <c r="I185" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J185" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="186" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>1571</v>
       </c>
@@ -7199,8 +7903,11 @@
       <c r="I186" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J186" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>1571</v>
       </c>
@@ -7228,8 +7935,11 @@
       <c r="I187" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J187" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>1571</v>
       </c>
@@ -7257,8 +7967,11 @@
       <c r="I188" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J188" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>1571</v>
       </c>
@@ -7286,8 +7999,11 @@
       <c r="I189" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J189" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="190" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>1571</v>
       </c>
@@ -7315,8 +8031,11 @@
       <c r="I190" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J190" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="191" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>1571</v>
       </c>
@@ -7344,8 +8063,11 @@
       <c r="I191" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J191" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="192" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>1571</v>
       </c>
@@ -7373,8 +8095,11 @@
       <c r="I192" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J192" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="193" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>1571</v>
       </c>
@@ -7402,8 +8127,11 @@
       <c r="I193" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J193" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="194" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>1571</v>
       </c>
@@ -7431,8 +8159,11 @@
       <c r="I194" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J194" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="195" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>1629</v>
       </c>
@@ -7460,8 +8191,11 @@
       <c r="I195" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J195" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="196" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>1629</v>
       </c>
@@ -7489,8 +8223,11 @@
       <c r="I196" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J196" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="197" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>1629</v>
       </c>
@@ -7518,8 +8255,11 @@
       <c r="I197" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J197" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="198" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>1629</v>
       </c>
@@ -7547,8 +8287,11 @@
       <c r="I198" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J198" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="199" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>1629</v>
       </c>
@@ -7576,8 +8319,11 @@
       <c r="I199" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J199" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="200" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>1629</v>
       </c>
@@ -7605,8 +8351,11 @@
       <c r="I200" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J200" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="201" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>1629</v>
       </c>
@@ -7634,8 +8383,11 @@
       <c r="I201" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J201" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="202" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>1809</v>
       </c>
@@ -7663,8 +8415,11 @@
       <c r="I202" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J202" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="203" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>1809</v>
       </c>
@@ -7692,8 +8447,11 @@
       <c r="I203" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J203" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="204" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>1809</v>
       </c>
@@ -7721,8 +8479,11 @@
       <c r="I204" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J204" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="205" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>1809</v>
       </c>
@@ -7750,8 +8511,11 @@
       <c r="I205" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J205" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="206" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>1809</v>
       </c>
@@ -7779,8 +8543,11 @@
       <c r="I206" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J206" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="207" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>1809</v>
       </c>
@@ -7808,8 +8575,11 @@
       <c r="I207" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J207" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="208" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>1809</v>
       </c>
@@ -7837,8 +8607,11 @@
       <c r="I208" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J208" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="209" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>1809</v>
       </c>
@@ -7866,8 +8639,11 @@
       <c r="I209" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J209" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>1809</v>
       </c>
@@ -7895,8 +8671,11 @@
       <c r="I210" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J210" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="211" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>1809</v>
       </c>
@@ -7924,8 +8703,11 @@
       <c r="I211" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J211" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="212" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>1809</v>
       </c>
@@ -7953,8 +8735,11 @@
       <c r="I212" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J212" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="213" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>1809</v>
       </c>
@@ -7982,8 +8767,11 @@
       <c r="I213" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J213" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="214" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>1228</v>
       </c>
@@ -8011,8 +8799,11 @@
       <c r="I214" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J214" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="215" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>1228</v>
       </c>
@@ -8040,8 +8831,11 @@
       <c r="I215" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J215" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="216" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>1745</v>
       </c>
@@ -8069,8 +8863,11 @@
       <c r="I216" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J216" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="217" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>1745</v>
       </c>
@@ -8098,8 +8895,11 @@
       <c r="I217" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J217" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="218" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>1745</v>
       </c>
@@ -8127,8 +8927,11 @@
       <c r="I218" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J218" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="219" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>1745</v>
       </c>
@@ -8156,8 +8959,11 @@
       <c r="I219" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J219" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="220" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>1745</v>
       </c>
@@ -8185,8 +8991,11 @@
       <c r="I220" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J220" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="221" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>1745</v>
       </c>
@@ -8214,8 +9023,11 @@
       <c r="I221" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J221" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="222" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>1745</v>
       </c>
@@ -8243,8 +9055,11 @@
       <c r="I222" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J222" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="223" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>1745</v>
       </c>
@@ -8272,8 +9087,11 @@
       <c r="I223" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J223" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="224" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>1745</v>
       </c>
@@ -8301,8 +9119,11 @@
       <c r="I224" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J224" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="225" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>1745</v>
       </c>
@@ -8330,8 +9151,11 @@
       <c r="I225" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J225" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="226" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>1745</v>
       </c>
@@ -8359,8 +9183,11 @@
       <c r="I226" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J226" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>1745</v>
       </c>
@@ -8388,8 +9215,11 @@
       <c r="I227" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J227" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="228" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>1745</v>
       </c>
@@ -8417,8 +9247,11 @@
       <c r="I228" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J228" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="229" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>1745</v>
       </c>
@@ -8446,8 +9279,11 @@
       <c r="I229" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J229" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="230" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>1745</v>
       </c>
@@ -8475,8 +9311,11 @@
       <c r="I230" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J230" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="231" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>1745</v>
       </c>
@@ -8504,8 +9343,11 @@
       <c r="I231" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J231" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="232" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>1745</v>
       </c>
@@ -8533,8 +9375,11 @@
       <c r="I232" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J232" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="233" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>1745</v>
       </c>
@@ -8562,8 +9407,11 @@
       <c r="I233" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J233" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="234" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>1745</v>
       </c>
@@ -8591,8 +9439,11 @@
       <c r="I234" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J234" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="235" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>1745</v>
       </c>
@@ -8620,8 +9471,11 @@
       <c r="I235" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J235" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="236" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>1745</v>
       </c>
@@ -8649,8 +9503,11 @@
       <c r="I236" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J236" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="237" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>1745</v>
       </c>
@@ -8678,8 +9535,11 @@
       <c r="I237" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J237" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="238" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>1745</v>
       </c>
@@ -8707,8 +9567,11 @@
       <c r="I238" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J238" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="239" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>1745</v>
       </c>
@@ -8736,8 +9599,11 @@
       <c r="I239" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J239" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="240" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>1745</v>
       </c>
@@ -8765,8 +9631,11 @@
       <c r="I240" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J240" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="241" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>1230</v>
       </c>
@@ -8794,8 +9663,11 @@
       <c r="I241" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J241" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="242" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>2207</v>
       </c>
@@ -8823,8 +9695,11 @@
       <c r="I242" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J242" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="243" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>2207</v>
       </c>
@@ -8852,8 +9727,11 @@
       <c r="I243" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J243" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="244" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>2207</v>
       </c>
@@ -8881,8 +9759,11 @@
       <c r="I244" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J244" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="245" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>2207</v>
       </c>
@@ -8910,8 +9791,11 @@
       <c r="I245" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J245" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="246" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>2126</v>
       </c>
@@ -8939,8 +9823,11 @@
       <c r="I246" t="s">
         <v>448</v>
       </c>
-    </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J246" s="3" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="247" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>2126</v>
       </c>
@@ -8968,8 +9855,11 @@
       <c r="I247" t="s">
         <v>448</v>
       </c>
-    </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J247" s="3" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="248" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>2126</v>
       </c>
@@ -8997,8 +9887,11 @@
       <c r="I248" t="s">
         <v>448</v>
       </c>
-    </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J248" s="3" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="249" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>2244</v>
       </c>
@@ -9026,8 +9919,11 @@
       <c r="I249" t="s">
         <v>449</v>
       </c>
-    </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J249" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="250" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>2244</v>
       </c>
@@ -9055,8 +9951,11 @@
       <c r="I250" t="s">
         <v>449</v>
       </c>
-    </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J250" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="251" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>2244</v>
       </c>
@@ -9084,8 +9983,11 @@
       <c r="I251" t="s">
         <v>449</v>
       </c>
-    </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J251" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="252" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>2244</v>
       </c>
@@ -9113,8 +10015,11 @@
       <c r="I252" t="s">
         <v>449</v>
       </c>
-    </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J252" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="253" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>2244</v>
       </c>
@@ -9142,8 +10047,11 @@
       <c r="I253" t="s">
         <v>449</v>
       </c>
-    </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J253" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="254" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>1950</v>
       </c>
@@ -9171,8 +10079,11 @@
       <c r="I254" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J254" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="255" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>1950</v>
       </c>
@@ -9200,8 +10111,11 @@
       <c r="I255" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J255" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="256" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>2255</v>
       </c>
@@ -9229,8 +10143,11 @@
       <c r="I256" t="s">
         <v>451</v>
       </c>
-    </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J256" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="257" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>2250</v>
       </c>
@@ -9258,8 +10175,11 @@
       <c r="I257" t="s">
         <v>452</v>
       </c>
-    </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J257" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="258" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>2250</v>
       </c>
@@ -9287,8 +10207,11 @@
       <c r="I258" t="s">
         <v>452</v>
       </c>
-    </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J258" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="259" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>2250</v>
       </c>
@@ -9316,8 +10239,11 @@
       <c r="I259" t="s">
         <v>452</v>
       </c>
-    </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J259" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="260" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>2250</v>
       </c>
@@ -9345,8 +10271,11 @@
       <c r="I260" t="s">
         <v>452</v>
       </c>
-    </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J260" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="261" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>2250</v>
       </c>
@@ -9374,8 +10303,11 @@
       <c r="I261" t="s">
         <v>452</v>
       </c>
-    </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J261" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="262" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>2250</v>
       </c>
@@ -9402,6 +10334,9 @@
       </c>
       <c r="I262" t="s">
         <v>452</v>
+      </c>
+      <c r="J262" t="s">
+        <v>501</v>
       </c>
     </row>
   </sheetData>
@@ -9416,18 +10351,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9545,18 +10480,18 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{034CDF24-425D-4892-AB7F-AACD3A1CB9F3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9975CE17-A2BF-4108-83DD-AD872CF67E1E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9975CE17-A2BF-4108-83DD-AD872CF67E1E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{034CDF24-425D-4892-AB7F-AACD3A1CB9F3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data/existing/판매중_상품구성_사업방법서_매핑.xlsx
+++ b/data/existing/판매중_상품구성_사업방법서_매핑.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\claudecsw\ruleautomatker\data\existing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33AE1D88-8639-48F9-B030-CB186CCCCC31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D701C6C-34A3-40D0-A349-D649750F4EAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51480" yWindow="30" windowWidth="51840" windowHeight="21120" xr2:uid="{364CA86F-2012-40A9-A884-5853FC3C1200}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{364CA86F-2012-40A9-A884-5853FC3C1200}"/>
   </bookViews>
   <sheets>
     <sheet name="보종코드_상품코드_매핑" sheetId="2" r:id="rId1"/>
@@ -8832,7 +8832,7 @@
         <v>445</v>
       </c>
       <c r="J215" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.3">
@@ -10360,12 +10360,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="MetaDocumentWS" ma:contentTypeID="0x01010002328573F07347D9A7800BDA19699CC200DE8F1DF1BF4211488DA32D5AC68DFB95" ma:contentTypeVersion="0" ma:contentTypeDescription="Metadata Content Type(Workshare)" ma:contentTypeScope="" ma:versionID="ea2efc4932be20cf5e8fe2ec0517f4d4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b6142cc285753f069fe6237cbe592e30">
     <xsd:element name="properties">
@@ -10479,6 +10473,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9975CE17-A2BF-4108-83DD-AD872CF67E1E}">
   <ds:schemaRefs>
@@ -10488,15 +10488,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{034CDF24-425D-4892-AB7F-AACD3A1CB9F3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D297E724-C9ED-40B8-8790-2B8BEFF24B33}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10510,4 +10501,13 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{034CDF24-425D-4892-AB7F-AACD3A1CB9F3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>